--- a/np_detachment/np_sorted_file.xlsx
+++ b/np_detachment/np_sorted_file.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:H172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,12 +424,37 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>fileNum</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>simulation time</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
-          <t>bound particles</t>
+          <t>lig_x</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>lig_y</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>lig_z</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Number of Bonds Left</t>
         </is>
       </c>
     </row>
@@ -438,10 +463,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="C2" t="n">
-        <v>100.5780346820809</v>
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.065265</v>
+      </c>
+      <c r="E2" t="n">
+        <v>523.310434</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-48.01272</v>
+      </c>
+      <c r="G2" t="n">
+        <v>435.651627</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -449,10 +489,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>88.05031446540829</v>
+        <v>111</v>
       </c>
       <c r="C3" t="n">
-        <v>30.96957138183007</v>
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.089642</v>
+      </c>
+      <c r="E3" t="n">
+        <v>451.1393019999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>269.322061</v>
+      </c>
+      <c r="G3" t="n">
+        <v>413.148644</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -460,10 +515,25 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>138.3647798742135</v>
+        <v>154</v>
       </c>
       <c r="C4" t="n">
-        <v>16.62704038971898</v>
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.4325699999999999</v>
+      </c>
+      <c r="E4" t="n">
+        <v>476.575302</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-221.21812</v>
+      </c>
+      <c r="G4" t="n">
+        <v>190.81415</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -471,10 +541,25 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>183.6477987421381</v>
+        <v>102</v>
       </c>
       <c r="C5" t="n">
-        <v>10.37772203439125</v>
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.56933</v>
+      </c>
+      <c r="E5" t="n">
+        <v>413.207441</v>
+      </c>
+      <c r="F5" t="n">
+        <v>324.376283</v>
+      </c>
+      <c r="G5" t="n">
+        <v>462.074933</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -482,10 +567,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>223.8993710691823</v>
+        <v>136</v>
       </c>
       <c r="C6" t="n">
-        <v>8.059766604864221</v>
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.67748</v>
+      </c>
+      <c r="E6" t="n">
+        <v>474.359113</v>
+      </c>
+      <c r="F6" t="n">
+        <v>225.681311</v>
+      </c>
+      <c r="G6" t="n">
+        <v>182.672466</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -493,10 +593,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>269.1823899371067</v>
+        <v>127</v>
       </c>
       <c r="C7" t="n">
-        <v>5.74108408768677</v>
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.0448</v>
+      </c>
+      <c r="E7" t="n">
+        <v>521.801728</v>
+      </c>
+      <c r="F7" t="n">
+        <v>60.40944200000001</v>
+      </c>
+      <c r="G7" t="n">
+        <v>321.476931</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -504,10 +619,25 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>269.1823899371067</v>
+        <v>31</v>
       </c>
       <c r="C8" t="n">
-        <v>5.74108408768677</v>
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.2789</v>
+      </c>
+      <c r="E8" t="n">
+        <v>258.142471</v>
+      </c>
+      <c r="F8" t="n">
+        <v>457.280632</v>
+      </c>
+      <c r="G8" t="n">
+        <v>244.808561</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -515,10 +645,4263 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>354.7169811320754</v>
+        <v>103</v>
       </c>
       <c r="C9" t="n">
-        <v>4.80386810630021</v>
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.3573</v>
+      </c>
+      <c r="E9" t="n">
+        <v>236.772067</v>
+      </c>
+      <c r="F9" t="n">
+        <v>469.421912</v>
+      </c>
+      <c r="G9" t="n">
+        <v>148.454015</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>86</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="E10" t="n">
+        <v>513.621204</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-109.098333</v>
+      </c>
+      <c r="G10" t="n">
+        <v>317.024926</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>26</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.3144</v>
+      </c>
+      <c r="E11" t="n">
+        <v>521.6795139999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>62.747659</v>
+      </c>
+      <c r="G11" t="n">
+        <v>239.312962</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>96</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.3453</v>
+      </c>
+      <c r="E12" t="n">
+        <v>510.594192</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-122.925855</v>
+      </c>
+      <c r="G12" t="n">
+        <v>206.433301</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>106</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="E13" t="n">
+        <v>522.9976</v>
+      </c>
+      <c r="F13" t="n">
+        <v>47.060479</v>
+      </c>
+      <c r="G13" t="n">
+        <v>435.713979</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>150</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.6377</v>
+      </c>
+      <c r="E14" t="n">
+        <v>508.787379</v>
+      </c>
+      <c r="F14" t="n">
+        <v>129.595181</v>
+      </c>
+      <c r="G14" t="n">
+        <v>304.480705</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>75</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.953</v>
+      </c>
+      <c r="E15" t="n">
+        <v>501.638135</v>
+      </c>
+      <c r="F15" t="n">
+        <v>156.409213</v>
+      </c>
+      <c r="G15" t="n">
+        <v>434.439681</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>44</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.2146</v>
+      </c>
+      <c r="E16" t="n">
+        <v>433.08091</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-298.539064</v>
+      </c>
+      <c r="G16" t="n">
+        <v>371.876423</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="n">
+        <v>146</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.2322</v>
+      </c>
+      <c r="E17" t="n">
+        <v>514.358103</v>
+      </c>
+      <c r="F17" t="n">
+        <v>111.317294</v>
+      </c>
+      <c r="G17" t="n">
+        <v>540.962005</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>180</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.2837</v>
+      </c>
+      <c r="E18" t="n">
+        <v>398.557273</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-341.855209</v>
+      </c>
+      <c r="G18" t="n">
+        <v>433.604871</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>134</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3.3575</v>
+      </c>
+      <c r="E19" t="n">
+        <v>516.56197</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-96.687341</v>
+      </c>
+      <c r="G19" t="n">
+        <v>179.587898</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>192</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3.6892</v>
+      </c>
+      <c r="E20" t="n">
+        <v>317.329868</v>
+      </c>
+      <c r="F20" t="n">
+        <v>418.465283</v>
+      </c>
+      <c r="G20" t="n">
+        <v>250.173135</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>156</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3.8394</v>
+      </c>
+      <c r="E21" t="n">
+        <v>150.563358</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-503.520888999999</v>
+      </c>
+      <c r="G21" t="n">
+        <v>449.207544</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="n">
+        <v>77</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4.1044</v>
+      </c>
+      <c r="E22" t="n">
+        <v>503.731568</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-149.337218</v>
+      </c>
+      <c r="G22" t="n">
+        <v>269.153026</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>42</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4.1386</v>
+      </c>
+      <c r="E23" t="n">
+        <v>485.767559</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-199.290587999999</v>
+      </c>
+      <c r="G23" t="n">
+        <v>225.675298</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
+        <v>186</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>4.6799</v>
+      </c>
+      <c r="E24" t="n">
+        <v>384.237281</v>
+      </c>
+      <c r="F24" t="n">
+        <v>358.01037</v>
+      </c>
+      <c r="G24" t="n">
+        <v>460.239554</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4.9674</v>
+      </c>
+      <c r="E25" t="n">
+        <v>454.7988360000001</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-262.497362</v>
+      </c>
+      <c r="G25" t="n">
+        <v>271.258786</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="n">
+        <v>164</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>5.3843</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-386.393872</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-355.756493</v>
+      </c>
+      <c r="G26" t="n">
+        <v>314.036983</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>5.5104</v>
+      </c>
+      <c r="E27" t="n">
+        <v>444.413654</v>
+      </c>
+      <c r="F27" t="n">
+        <v>279.735369</v>
+      </c>
+      <c r="G27" t="n">
+        <v>207.403734</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>24</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>6.2219</v>
+      </c>
+      <c r="E28" t="n">
+        <v>513.226462</v>
+      </c>
+      <c r="F28" t="n">
+        <v>111.147953</v>
+      </c>
+      <c r="G28" t="n">
+        <v>275.547382</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="n">
+        <v>53</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>6.2412</v>
+      </c>
+      <c r="E29" t="n">
+        <v>504.702413</v>
+      </c>
+      <c r="F29" t="n">
+        <v>145.232646</v>
+      </c>
+      <c r="G29" t="n">
+        <v>183.417255</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="n">
+        <v>74</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>6.2662</v>
+      </c>
+      <c r="E30" t="n">
+        <v>521.197258</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-66.026765</v>
+      </c>
+      <c r="G30" t="n">
+        <v>323.083445</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="n">
+        <v>15</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>6.2969</v>
+      </c>
+      <c r="E31" t="n">
+        <v>458.385548</v>
+      </c>
+      <c r="F31" t="n">
+        <v>256.202031</v>
+      </c>
+      <c r="G31" t="n">
+        <v>152.864661</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="n">
+        <v>65</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>6.6816</v>
+      </c>
+      <c r="E32" t="n">
+        <v>463.2744</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-248.087048</v>
+      </c>
+      <c r="G32" t="n">
+        <v>213.045746</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="n">
+        <v>7</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>7.1096</v>
+      </c>
+      <c r="E33" t="n">
+        <v>509.799065</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-125.949003</v>
+      </c>
+      <c r="G33" t="n">
+        <v>388.125336</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="n">
+        <v>61</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>7.1385</v>
+      </c>
+      <c r="E34" t="n">
+        <v>484.017883</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-204.612762</v>
+      </c>
+      <c r="G34" t="n">
+        <v>512.472573</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="n">
+        <v>104</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>7.2446</v>
+      </c>
+      <c r="E35" t="n">
+        <v>525.4323910000001</v>
+      </c>
+      <c r="F35" t="n">
+        <v>5.145014</v>
+      </c>
+      <c r="G35" t="n">
+        <v>167.032385</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="n">
+        <v>131</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>7.6738</v>
+      </c>
+      <c r="E36" t="n">
+        <v>212.379884</v>
+      </c>
+      <c r="F36" t="n">
+        <v>481.245814</v>
+      </c>
+      <c r="G36" t="n">
+        <v>222.546196</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="n">
+        <v>172</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>7.6852</v>
+      </c>
+      <c r="E37" t="n">
+        <v>461.1068570000001</v>
+      </c>
+      <c r="F37" t="n">
+        <v>252.086435</v>
+      </c>
+      <c r="G37" t="n">
+        <v>118.314463</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="n">
+        <v>25</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>7.8274</v>
+      </c>
+      <c r="E38" t="n">
+        <v>437.052917</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-291.361152</v>
+      </c>
+      <c r="G38" t="n">
+        <v>358.086972</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="n">
+        <v>197</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>8.460100000000001</v>
+      </c>
+      <c r="E39" t="n">
+        <v>470.139405</v>
+      </c>
+      <c r="F39" t="n">
+        <v>234.257399</v>
+      </c>
+      <c r="G39" t="n">
+        <v>377.901527</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="n">
+        <v>121</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>8.581200000000001</v>
+      </c>
+      <c r="E40" t="n">
+        <v>521.558161</v>
+      </c>
+      <c r="F40" t="n">
+        <v>63.53105600000001</v>
+      </c>
+      <c r="G40" t="n">
+        <v>355.492146</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>9.017799999999999</v>
+      </c>
+      <c r="E41" t="n">
+        <v>513.1105299999999</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-114.000135</v>
+      </c>
+      <c r="G41" t="n">
+        <v>208.596961</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="n">
+        <v>153</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>9.354799999999999</v>
+      </c>
+      <c r="E42" t="n">
+        <v>506.3614519999999</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-140.285059</v>
+      </c>
+      <c r="G42" t="n">
+        <v>226.917937</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="n">
+        <v>169</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>9.775499999999999</v>
+      </c>
+      <c r="E43" t="n">
+        <v>525.1931039999999</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-13.044069</v>
+      </c>
+      <c r="G43" t="n">
+        <v>292.365262</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="n">
+        <v>49</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>9.805999999999999</v>
+      </c>
+      <c r="E44" t="n">
+        <v>524.992111</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-11.217683</v>
+      </c>
+      <c r="G44" t="n">
+        <v>467.701654</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="n">
+        <v>37</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="n">
+        <v>10.149</v>
+      </c>
+      <c r="E45" t="n">
+        <v>421.837417</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-313.062689</v>
+      </c>
+      <c r="G45" t="n">
+        <v>221.963516</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="n">
+        <v>63</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>10.952</v>
+      </c>
+      <c r="E46" t="n">
+        <v>521.376576</v>
+      </c>
+      <c r="F46" t="n">
+        <v>62.397933</v>
+      </c>
+      <c r="G46" t="n">
+        <v>343.534782</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="n">
+        <v>190</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="E47" t="n">
+        <v>523.5146589999999</v>
+      </c>
+      <c r="F47" t="n">
+        <v>43.68411500000001</v>
+      </c>
+      <c r="G47" t="n">
+        <v>263.961486</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="n">
+        <v>118</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
+        <v>11.462</v>
+      </c>
+      <c r="E48" t="n">
+        <v>521.928559</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-60.677347</v>
+      </c>
+      <c r="G48" t="n">
+        <v>165.335847</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="n">
+        <v>90</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>12.032</v>
+      </c>
+      <c r="E49" t="n">
+        <v>470.639876</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-232.859531</v>
+      </c>
+      <c r="G49" t="n">
+        <v>371.890682</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="n">
+        <v>72</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
+        <v>12.515</v>
+      </c>
+      <c r="E50" t="n">
+        <v>490.407191</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-189.169043</v>
+      </c>
+      <c r="G50" t="n">
+        <v>281.719915</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="n">
+        <v>183</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>12.853</v>
+      </c>
+      <c r="E51" t="n">
+        <v>472.6667860000001</v>
+      </c>
+      <c r="F51" t="n">
+        <v>229.208428</v>
+      </c>
+      <c r="G51" t="n">
+        <v>795.390311</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="n">
+        <v>174</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>12.873</v>
+      </c>
+      <c r="E52" t="n">
+        <v>519.8025389999999</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-74.81963499999991</v>
+      </c>
+      <c r="G52" t="n">
+        <v>412.719636</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="n">
+        <v>119</v>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>13.299</v>
+      </c>
+      <c r="E53" t="n">
+        <v>521.704197</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-60.4934469999999</v>
+      </c>
+      <c r="G53" t="n">
+        <v>264.073917</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="n">
+        <v>27</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="n">
+        <v>13.399</v>
+      </c>
+      <c r="E54" t="n">
+        <v>514.624855</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-104.99075</v>
+      </c>
+      <c r="G54" t="n">
+        <v>222.499188</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="n">
+        <v>80</v>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="n">
+        <v>13.49</v>
+      </c>
+      <c r="E55" t="n">
+        <v>513.2371860000001</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-113.174575</v>
+      </c>
+      <c r="G55" t="n">
+        <v>388.342413</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="n">
+        <v>41</v>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="n">
+        <v>13.659</v>
+      </c>
+      <c r="E56" t="n">
+        <v>445.473613</v>
+      </c>
+      <c r="F56" t="n">
+        <v>278.111524</v>
+      </c>
+      <c r="G56" t="n">
+        <v>334.249344</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="n">
+        <v>123</v>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="n">
+        <v>14.237</v>
+      </c>
+      <c r="E57" t="n">
+        <v>434.1942360000001</v>
+      </c>
+      <c r="F57" t="n">
+        <v>297.024889</v>
+      </c>
+      <c r="G57" t="n">
+        <v>348.47855</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="n">
+        <v>196</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>14.281</v>
+      </c>
+      <c r="E58" t="n">
+        <v>402.213988</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-337.522832</v>
+      </c>
+      <c r="G58" t="n">
+        <v>245.628355</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="n">
+        <v>84</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="n">
+        <v>14.467</v>
+      </c>
+      <c r="E59" t="n">
+        <v>484.219855</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-203.386269</v>
+      </c>
+      <c r="G59" t="n">
+        <v>183.464893</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="n">
+        <v>14.748</v>
+      </c>
+      <c r="E60" t="n">
+        <v>411.909092</v>
+      </c>
+      <c r="F60" t="n">
+        <v>325.801534</v>
+      </c>
+      <c r="G60" t="n">
+        <v>572.284947</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="n">
+        <v>135</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="n">
+        <v>15.369</v>
+      </c>
+      <c r="E61" t="n">
+        <v>493.317967</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-183.02835</v>
+      </c>
+      <c r="G61" t="n">
+        <v>322.586961</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="n">
+        <v>3</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="n">
+        <v>15.474</v>
+      </c>
+      <c r="E62" t="n">
+        <v>516.941601</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-93.914238</v>
+      </c>
+      <c r="G62" t="n">
+        <v>395.190428</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="n">
+        <v>177</v>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="n">
+        <v>16.462</v>
+      </c>
+      <c r="E63" t="n">
+        <v>400.161105</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-342.144717</v>
+      </c>
+      <c r="G63" t="n">
+        <v>309.674022</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="n">
+        <v>92</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="n">
+        <v>16.809</v>
+      </c>
+      <c r="E64" t="n">
+        <v>516.05261</v>
+      </c>
+      <c r="F64" t="n">
+        <v>97.274503</v>
+      </c>
+      <c r="G64" t="n">
+        <v>138.475118</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="n">
+        <v>82</v>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="n">
+        <v>17.44</v>
+      </c>
+      <c r="E65" t="n">
+        <v>519.286962</v>
+      </c>
+      <c r="F65" t="n">
+        <v>-77.27350300000001</v>
+      </c>
+      <c r="G65" t="n">
+        <v>195.933672</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="n">
+        <v>43</v>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="n">
+        <v>17.512</v>
+      </c>
+      <c r="E66" t="n">
+        <v>499.212332</v>
+      </c>
+      <c r="F66" t="n">
+        <v>162.891364</v>
+      </c>
+      <c r="G66" t="n">
+        <v>532.91022</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="n">
+        <v>147</v>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="n">
+        <v>17.515</v>
+      </c>
+      <c r="E67" t="n">
+        <v>508.954354</v>
+      </c>
+      <c r="F67" t="n">
+        <v>-130.030677</v>
+      </c>
+      <c r="G67" t="n">
+        <v>227.272186</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="n">
+        <v>73</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="n">
+        <v>17.617</v>
+      </c>
+      <c r="E68" t="n">
+        <v>515.633728</v>
+      </c>
+      <c r="F68" t="n">
+        <v>-101.646453</v>
+      </c>
+      <c r="G68" t="n">
+        <v>312.008076</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="n">
+        <v>8</v>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" t="n">
+        <v>17.931</v>
+      </c>
+      <c r="E69" t="n">
+        <v>423.911585</v>
+      </c>
+      <c r="F69" t="n">
+        <v>-309.843288</v>
+      </c>
+      <c r="G69" t="n">
+        <v>277.804245</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="n">
+        <v>62</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="n">
+        <v>19.861</v>
+      </c>
+      <c r="E70" t="n">
+        <v>478.76</v>
+      </c>
+      <c r="F70" t="n">
+        <v>-217.081296</v>
+      </c>
+      <c r="G70" t="n">
+        <v>193.27419</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="n">
+        <v>161</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="n">
+        <v>19.924</v>
+      </c>
+      <c r="E71" t="n">
+        <v>524.882845</v>
+      </c>
+      <c r="F71" t="n">
+        <v>29.940826</v>
+      </c>
+      <c r="G71" t="n">
+        <v>331.967323</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="n">
+        <v>120</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="n">
+        <v>20.102</v>
+      </c>
+      <c r="E72" t="n">
+        <v>487.8185610000001</v>
+      </c>
+      <c r="F72" t="n">
+        <v>195.889129</v>
+      </c>
+      <c r="G72" t="n">
+        <v>159.905217</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="n">
+        <v>60</v>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="n">
+        <v>20.973</v>
+      </c>
+      <c r="E73" t="n">
+        <v>302.581157</v>
+      </c>
+      <c r="F73" t="n">
+        <v>429.0842730000001</v>
+      </c>
+      <c r="G73" t="n">
+        <v>412.588087</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="n">
+        <v>112</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="n">
+        <v>21.044</v>
+      </c>
+      <c r="E74" t="n">
+        <v>502.517621</v>
+      </c>
+      <c r="F74" t="n">
+        <v>152.812783</v>
+      </c>
+      <c r="G74" t="n">
+        <v>253.54675</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="n">
+        <v>200</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="n">
+        <v>21.613</v>
+      </c>
+      <c r="E75" t="n">
+        <v>459.534755</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-254.020504</v>
+      </c>
+      <c r="G75" t="n">
+        <v>371.562006</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="n">
+        <v>107</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="n">
+        <v>22.394</v>
+      </c>
+      <c r="E76" t="n">
+        <v>525.378548</v>
+      </c>
+      <c r="F76" t="n">
+        <v>-14.628501</v>
+      </c>
+      <c r="G76" t="n">
+        <v>347.494411</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="n">
+        <v>152</v>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="n">
+        <v>22.415</v>
+      </c>
+      <c r="E77" t="n">
+        <v>440.176325</v>
+      </c>
+      <c r="F77" t="n">
+        <v>286.26591</v>
+      </c>
+      <c r="G77" t="n">
+        <v>381.414821</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="n">
+        <v>173</v>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="E78" t="n">
+        <v>525.354319</v>
+      </c>
+      <c r="F78" t="n">
+        <v>7.971756</v>
+      </c>
+      <c r="G78" t="n">
+        <v>234.573331</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="n">
+        <v>138</v>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="n">
+        <v>22.997</v>
+      </c>
+      <c r="E79" t="n">
+        <v>509.235611</v>
+      </c>
+      <c r="F79" t="n">
+        <v>-130.821606</v>
+      </c>
+      <c r="G79" t="n">
+        <v>129.02494</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="n">
+        <v>148</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="n">
+        <v>23.485</v>
+      </c>
+      <c r="E80" t="n">
+        <v>512.058692</v>
+      </c>
+      <c r="F80" t="n">
+        <v>116.317893</v>
+      </c>
+      <c r="G80" t="n">
+        <v>142.875694</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="n">
+        <v>69</v>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="n">
+        <v>23.533</v>
+      </c>
+      <c r="E81" t="n">
+        <v>442.028229</v>
+      </c>
+      <c r="F81" t="n">
+        <v>-283.675071</v>
+      </c>
+      <c r="G81" t="n">
+        <v>196.50026</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="n">
+        <v>2</v>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="n">
+        <v>23.824</v>
+      </c>
+      <c r="E82" t="n">
+        <v>523.766795</v>
+      </c>
+      <c r="F82" t="n">
+        <v>42.921676</v>
+      </c>
+      <c r="G82" t="n">
+        <v>304.421742</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="n">
+        <v>33</v>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="n">
+        <v>23.86</v>
+      </c>
+      <c r="E83" t="n">
+        <v>474.578364</v>
+      </c>
+      <c r="F83" t="n">
+        <v>-225.237870999999</v>
+      </c>
+      <c r="G83" t="n">
+        <v>429.151945</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="n">
+        <v>160</v>
+      </c>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" t="n">
+        <v>25.84</v>
+      </c>
+      <c r="E84" t="n">
+        <v>515.0161419999999</v>
+      </c>
+      <c r="F84" t="n">
+        <v>105.59326</v>
+      </c>
+      <c r="G84" t="n">
+        <v>175.939585</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="n">
+        <v>109</v>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="n">
+        <v>27.321</v>
+      </c>
+      <c r="E85" t="n">
+        <v>524.17246</v>
+      </c>
+      <c r="F85" t="n">
+        <v>30.47681</v>
+      </c>
+      <c r="G85" t="n">
+        <v>211.096634</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="n">
+        <v>39</v>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="n">
+        <v>27.762</v>
+      </c>
+      <c r="E86" t="n">
+        <v>495.503813</v>
+      </c>
+      <c r="F86" t="n">
+        <v>-174.775537</v>
+      </c>
+      <c r="G86" t="n">
+        <v>452.9287240000001</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="n">
+        <v>145</v>
+      </c>
+      <c r="C87" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" t="n">
+        <v>28.321</v>
+      </c>
+      <c r="E87" t="n">
+        <v>325.696537</v>
+      </c>
+      <c r="F87" t="n">
+        <v>412.178594</v>
+      </c>
+      <c r="G87" t="n">
+        <v>419.860359</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="n">
+        <v>94</v>
+      </c>
+      <c r="C88" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" t="n">
+        <v>29.622</v>
+      </c>
+      <c r="E88" t="n">
+        <v>524.334072</v>
+      </c>
+      <c r="F88" t="n">
+        <v>29.608008</v>
+      </c>
+      <c r="G88" t="n">
+        <v>416.266854</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="n">
+        <v>95</v>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" t="n">
+        <v>31.431</v>
+      </c>
+      <c r="E89" t="n">
+        <v>440.207404</v>
+      </c>
+      <c r="F89" t="n">
+        <v>-286.259953</v>
+      </c>
+      <c r="G89" t="n">
+        <v>514.469736</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="n">
+        <v>195</v>
+      </c>
+      <c r="C90" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" t="n">
+        <v>32.009</v>
+      </c>
+      <c r="E90" t="n">
+        <v>485.014777</v>
+      </c>
+      <c r="F90" t="n">
+        <v>-204.026574</v>
+      </c>
+      <c r="G90" t="n">
+        <v>201.548584</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="n">
+        <v>68</v>
+      </c>
+      <c r="C91" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" t="n">
+        <v>32.267</v>
+      </c>
+      <c r="E91" t="n">
+        <v>490.600139</v>
+      </c>
+      <c r="F91" t="n">
+        <v>-187.066714</v>
+      </c>
+      <c r="G91" t="n">
+        <v>124.237822</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="n">
+        <v>36</v>
+      </c>
+      <c r="C92" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" t="n">
+        <v>32.743</v>
+      </c>
+      <c r="E92" t="n">
+        <v>503.679352</v>
+      </c>
+      <c r="F92" t="n">
+        <v>-149.59656</v>
+      </c>
+      <c r="G92" t="n">
+        <v>173.001125</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="n">
+        <v>51</v>
+      </c>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="n">
+        <v>34.891</v>
+      </c>
+      <c r="E93" t="n">
+        <v>525.028067</v>
+      </c>
+      <c r="F93" t="n">
+        <v>13.537286</v>
+      </c>
+      <c r="G93" t="n">
+        <v>125.750821</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="n">
+        <v>78</v>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" t="n">
+        <v>35.217</v>
+      </c>
+      <c r="E94" t="n">
+        <v>347.826212</v>
+      </c>
+      <c r="F94" t="n">
+        <v>-393.954563</v>
+      </c>
+      <c r="G94" t="n">
+        <v>194.336163</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="n">
+        <v>182</v>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="n">
+        <v>35.555</v>
+      </c>
+      <c r="E95" t="n">
+        <v>401.068258</v>
+      </c>
+      <c r="F95" t="n">
+        <v>-339.435694</v>
+      </c>
+      <c r="G95" t="n">
+        <v>446.404175</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="n">
+        <v>193</v>
+      </c>
+      <c r="C96" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" t="n">
+        <v>35.94</v>
+      </c>
+      <c r="E96" t="n">
+        <v>394.857591</v>
+      </c>
+      <c r="F96" t="n">
+        <v>-346.127379</v>
+      </c>
+      <c r="G96" t="n">
+        <v>209.957931</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="n">
+        <v>141</v>
+      </c>
+      <c r="C97" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" t="n">
+        <v>36.443</v>
+      </c>
+      <c r="E97" t="n">
+        <v>494.845534</v>
+      </c>
+      <c r="F97" t="n">
+        <v>177.748731</v>
+      </c>
+      <c r="G97" t="n">
+        <v>403.308401</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="n">
+        <v>189</v>
+      </c>
+      <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="n">
+        <v>37</v>
+      </c>
+      <c r="E98" t="n">
+        <v>486.755603</v>
+      </c>
+      <c r="F98" t="n">
+        <v>197.047162</v>
+      </c>
+      <c r="G98" t="n">
+        <v>129.834842</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="n">
+        <v>133</v>
+      </c>
+      <c r="C99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" t="n">
+        <v>37.363</v>
+      </c>
+      <c r="E99" t="n">
+        <v>522.9895309999999</v>
+      </c>
+      <c r="F99" t="n">
+        <v>47.352887</v>
+      </c>
+      <c r="G99" t="n">
+        <v>382.699873</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="n">
+        <v>162</v>
+      </c>
+      <c r="C100" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" t="n">
+        <v>37.436</v>
+      </c>
+      <c r="E100" t="n">
+        <v>-91.198198</v>
+      </c>
+      <c r="F100" t="n">
+        <v>517.151302</v>
+      </c>
+      <c r="G100" t="n">
+        <v>200.77912</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="n">
+        <v>168</v>
+      </c>
+      <c r="C101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" t="n">
+        <v>37.712</v>
+      </c>
+      <c r="E101" t="n">
+        <v>495.844814</v>
+      </c>
+      <c r="F101" t="n">
+        <v>174.573038</v>
+      </c>
+      <c r="G101" t="n">
+        <v>188.236384</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="n">
+        <v>110</v>
+      </c>
+      <c r="C102" t="n">
+        <v>1</v>
+      </c>
+      <c r="D102" t="n">
+        <v>38.119</v>
+      </c>
+      <c r="E102" t="n">
+        <v>517.197235</v>
+      </c>
+      <c r="F102" t="n">
+        <v>-90.69134099999999</v>
+      </c>
+      <c r="G102" t="n">
+        <v>405.040641</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="n">
+        <v>125</v>
+      </c>
+      <c r="C103" t="n">
+        <v>1</v>
+      </c>
+      <c r="D103" t="n">
+        <v>38.754</v>
+      </c>
+      <c r="E103" t="n">
+        <v>477.824679</v>
+      </c>
+      <c r="F103" t="n">
+        <v>-218.038925</v>
+      </c>
+      <c r="G103" t="n">
+        <v>199.136188</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="n">
+        <v>11</v>
+      </c>
+      <c r="C104" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" t="n">
+        <v>38.819</v>
+      </c>
+      <c r="E104" t="n">
+        <v>465.289686</v>
+      </c>
+      <c r="F104" t="n">
+        <v>-244.559798</v>
+      </c>
+      <c r="G104" t="n">
+        <v>249.842634</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="n">
+        <v>175</v>
+      </c>
+      <c r="C105" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" t="n">
+        <v>42.662</v>
+      </c>
+      <c r="E105" t="n">
+        <v>407.4832</v>
+      </c>
+      <c r="F105" t="n">
+        <v>331.25226</v>
+      </c>
+      <c r="G105" t="n">
+        <v>400.753101</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="n">
+        <v>126</v>
+      </c>
+      <c r="C106" t="n">
+        <v>1</v>
+      </c>
+      <c r="D106" t="n">
+        <v>43.761</v>
+      </c>
+      <c r="E106" t="n">
+        <v>477.273224</v>
+      </c>
+      <c r="F106" t="n">
+        <v>218.82235</v>
+      </c>
+      <c r="G106" t="n">
+        <v>354.379565</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="n">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="n">
+        <v>44.01300000000001</v>
+      </c>
+      <c r="E107" t="n">
+        <v>343.395947</v>
+      </c>
+      <c r="F107" t="n">
+        <v>-398.172033</v>
+      </c>
+      <c r="G107" t="n">
+        <v>384.912526</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="n">
+        <v>122</v>
+      </c>
+      <c r="C108" t="n">
+        <v>1</v>
+      </c>
+      <c r="D108" t="n">
+        <v>44.03</v>
+      </c>
+      <c r="E108" t="n">
+        <v>309.374836</v>
+      </c>
+      <c r="F108" t="n">
+        <v>424.496287</v>
+      </c>
+      <c r="G108" t="n">
+        <v>362.22542</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="n">
+        <v>70</v>
+      </c>
+      <c r="C109" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" t="n">
+        <v>46.123</v>
+      </c>
+      <c r="E109" t="n">
+        <v>499.437328</v>
+      </c>
+      <c r="F109" t="n">
+        <v>163.676345</v>
+      </c>
+      <c r="G109" t="n">
+        <v>192.302188</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="n">
+        <v>22</v>
+      </c>
+      <c r="C110" t="n">
+        <v>1</v>
+      </c>
+      <c r="D110" t="n">
+        <v>46.287</v>
+      </c>
+      <c r="E110" t="n">
+        <v>466.375777</v>
+      </c>
+      <c r="F110" t="n">
+        <v>-241.312179</v>
+      </c>
+      <c r="G110" t="n">
+        <v>645.518868</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="n">
+        <v>167</v>
+      </c>
+      <c r="C111" t="n">
+        <v>1</v>
+      </c>
+      <c r="D111" t="n">
+        <v>48.326</v>
+      </c>
+      <c r="E111" t="n">
+        <v>520.270519</v>
+      </c>
+      <c r="F111" t="n">
+        <v>-70.890725</v>
+      </c>
+      <c r="G111" t="n">
+        <v>311.19369</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="n">
+        <v>67</v>
+      </c>
+      <c r="C112" t="n">
+        <v>1</v>
+      </c>
+      <c r="D112" t="n">
+        <v>50.04600000000001</v>
+      </c>
+      <c r="E112" t="n">
+        <v>472.102285</v>
+      </c>
+      <c r="F112" t="n">
+        <v>-231.547133999999</v>
+      </c>
+      <c r="G112" t="n">
+        <v>206.140714</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="n">
+        <v>48</v>
+      </c>
+      <c r="C113" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" t="n">
+        <v>52.269</v>
+      </c>
+      <c r="E113" t="n">
+        <v>524.217129</v>
+      </c>
+      <c r="F113" t="n">
+        <v>36.73970300000001</v>
+      </c>
+      <c r="G113" t="n">
+        <v>147.288848</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="n">
+        <v>85</v>
+      </c>
+      <c r="C114" t="n">
+        <v>1</v>
+      </c>
+      <c r="D114" t="n">
+        <v>54.044</v>
+      </c>
+      <c r="E114" t="n">
+        <v>521.390634</v>
+      </c>
+      <c r="F114" t="n">
+        <v>64.69929499999999</v>
+      </c>
+      <c r="G114" t="n">
+        <v>410.329548</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="n">
+        <v>4</v>
+      </c>
+      <c r="C115" t="n">
+        <v>1</v>
+      </c>
+      <c r="D115" t="n">
+        <v>55.497</v>
+      </c>
+      <c r="E115" t="n">
+        <v>514.465189</v>
+      </c>
+      <c r="F115" t="n">
+        <v>107.065661</v>
+      </c>
+      <c r="G115" t="n">
+        <v>296.810468</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="n">
+        <v>13</v>
+      </c>
+      <c r="C116" t="n">
+        <v>1</v>
+      </c>
+      <c r="D116" t="n">
+        <v>55.76</v>
+      </c>
+      <c r="E116" t="n">
+        <v>377.369477</v>
+      </c>
+      <c r="F116" t="n">
+        <v>-365.05683</v>
+      </c>
+      <c r="G116" t="n">
+        <v>316.389103</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="n">
+        <v>58</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1</v>
+      </c>
+      <c r="D117" t="n">
+        <v>56.51</v>
+      </c>
+      <c r="E117" t="n">
+        <v>519.266557</v>
+      </c>
+      <c r="F117" t="n">
+        <v>80.228938</v>
+      </c>
+      <c r="G117" t="n">
+        <v>161.954713</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="n">
+        <v>45</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1</v>
+      </c>
+      <c r="D118" t="n">
+        <v>57.555</v>
+      </c>
+      <c r="E118" t="n">
+        <v>517.170475</v>
+      </c>
+      <c r="F118" t="n">
+        <v>-92.498604</v>
+      </c>
+      <c r="G118" t="n">
+        <v>386.899372</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="n">
+        <v>46</v>
+      </c>
+      <c r="C119" t="n">
+        <v>1</v>
+      </c>
+      <c r="D119" t="n">
+        <v>58.233</v>
+      </c>
+      <c r="E119" t="n">
+        <v>217.527593</v>
+      </c>
+      <c r="F119" t="n">
+        <v>-477.846117</v>
+      </c>
+      <c r="G119" t="n">
+        <v>324.272967</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="n">
+        <v>184</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1</v>
+      </c>
+      <c r="D120" t="n">
+        <v>61.681</v>
+      </c>
+      <c r="E120" t="n">
+        <v>494.407887</v>
+      </c>
+      <c r="F120" t="n">
+        <v>-181.361369</v>
+      </c>
+      <c r="G120" t="n">
+        <v>237.742519</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="n">
+        <v>91</v>
+      </c>
+      <c r="C121" t="n">
+        <v>1</v>
+      </c>
+      <c r="D121" t="n">
+        <v>62.122</v>
+      </c>
+      <c r="E121" t="n">
+        <v>525.0571660000001</v>
+      </c>
+      <c r="F121" t="n">
+        <v>-15.876593</v>
+      </c>
+      <c r="G121" t="n">
+        <v>140.464731</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="n">
+        <v>149</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1</v>
+      </c>
+      <c r="D122" t="n">
+        <v>65.292</v>
+      </c>
+      <c r="E122" t="n">
+        <v>497.650993</v>
+      </c>
+      <c r="F122" t="n">
+        <v>168.530653</v>
+      </c>
+      <c r="G122" t="n">
+        <v>322.609964</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="n">
+        <v>187</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1</v>
+      </c>
+      <c r="D123" t="n">
+        <v>67.36799999999999</v>
+      </c>
+      <c r="E123" t="n">
+        <v>463.193433</v>
+      </c>
+      <c r="F123" t="n">
+        <v>-247.740568</v>
+      </c>
+      <c r="G123" t="n">
+        <v>130.524294</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="n">
+        <v>142</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" t="n">
+        <v>70.26300000000001</v>
+      </c>
+      <c r="E124" t="n">
+        <v>476.099489</v>
+      </c>
+      <c r="F124" t="n">
+        <v>222.083699</v>
+      </c>
+      <c r="G124" t="n">
+        <v>407.418919</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="n">
+        <v>159</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1</v>
+      </c>
+      <c r="D125" t="n">
+        <v>71.048</v>
+      </c>
+      <c r="E125" t="n">
+        <v>501.77071</v>
+      </c>
+      <c r="F125" t="n">
+        <v>-155.285239</v>
+      </c>
+      <c r="G125" t="n">
+        <v>145.867526</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="n">
+        <v>89</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1</v>
+      </c>
+      <c r="D126" t="n">
+        <v>72.896</v>
+      </c>
+      <c r="E126" t="n">
+        <v>506.106032</v>
+      </c>
+      <c r="F126" t="n">
+        <v>-141.273875</v>
+      </c>
+      <c r="G126" t="n">
+        <v>568.168749</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="n">
+        <v>101</v>
+      </c>
+      <c r="C127" t="n">
+        <v>1</v>
+      </c>
+      <c r="D127" t="n">
+        <v>75.498</v>
+      </c>
+      <c r="E127" t="n">
+        <v>375.795788</v>
+      </c>
+      <c r="F127" t="n">
+        <v>-366.85854</v>
+      </c>
+      <c r="G127" t="n">
+        <v>143.065112</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="n">
+        <v>98</v>
+      </c>
+      <c r="C128" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" t="n">
+        <v>78.45699999999999</v>
+      </c>
+      <c r="E128" t="n">
+        <v>316.434008</v>
+      </c>
+      <c r="F128" t="n">
+        <v>419.13871</v>
+      </c>
+      <c r="G128" t="n">
+        <v>392.059615</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="n">
+        <v>64</v>
+      </c>
+      <c r="C129" t="n">
+        <v>1</v>
+      </c>
+      <c r="D129" t="n">
+        <v>78.99600000000001</v>
+      </c>
+      <c r="E129" t="n">
+        <v>518.521975</v>
+      </c>
+      <c r="F129" t="n">
+        <v>-83.601158</v>
+      </c>
+      <c r="G129" t="n">
+        <v>229.236567</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="n">
+        <v>117</v>
+      </c>
+      <c r="C130" t="n">
+        <v>1</v>
+      </c>
+      <c r="D130" t="n">
+        <v>80.492</v>
+      </c>
+      <c r="E130" t="n">
+        <v>385.683075</v>
+      </c>
+      <c r="F130" t="n">
+        <v>-357.530107</v>
+      </c>
+      <c r="G130" t="n">
+        <v>793.2176450000001</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="n">
+        <v>23</v>
+      </c>
+      <c r="C131" t="n">
+        <v>1</v>
+      </c>
+      <c r="D131" t="n">
+        <v>82.947</v>
+      </c>
+      <c r="E131" t="n">
+        <v>490.582685</v>
+      </c>
+      <c r="F131" t="n">
+        <v>-189.328332</v>
+      </c>
+      <c r="G131" t="n">
+        <v>508.895364</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="n">
+        <v>32</v>
+      </c>
+      <c r="C132" t="n">
+        <v>1</v>
+      </c>
+      <c r="D132" t="n">
+        <v>88.00700000000001</v>
+      </c>
+      <c r="E132" t="n">
+        <v>525.3268929999999</v>
+      </c>
+      <c r="F132" t="n">
+        <v>-0.5021</v>
+      </c>
+      <c r="G132" t="n">
+        <v>145.979109</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="n">
+        <v>191</v>
+      </c>
+      <c r="C133" t="n">
+        <v>1</v>
+      </c>
+      <c r="D133" t="n">
+        <v>89.616</v>
+      </c>
+      <c r="E133" t="n">
+        <v>396.575342</v>
+      </c>
+      <c r="F133" t="n">
+        <v>-344.249624</v>
+      </c>
+      <c r="G133" t="n">
+        <v>289.129589</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="n">
+        <v>129</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1</v>
+      </c>
+      <c r="D134" t="n">
+        <v>89.816</v>
+      </c>
+      <c r="E134" t="n">
+        <v>496.303349</v>
+      </c>
+      <c r="F134" t="n">
+        <v>-171.660968</v>
+      </c>
+      <c r="G134" t="n">
+        <v>647.060288</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="n">
+        <v>88</v>
+      </c>
+      <c r="C135" t="n">
+        <v>1</v>
+      </c>
+      <c r="D135" t="n">
+        <v>91.003</v>
+      </c>
+      <c r="E135" t="n">
+        <v>524.245075</v>
+      </c>
+      <c r="F135" t="n">
+        <v>-32.112013</v>
+      </c>
+      <c r="G135" t="n">
+        <v>229.999342</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="n">
+        <v>28</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1</v>
+      </c>
+      <c r="D136" t="n">
+        <v>91.291</v>
+      </c>
+      <c r="E136" t="n">
+        <v>503.654163</v>
+      </c>
+      <c r="F136" t="n">
+        <v>-148.624672</v>
+      </c>
+      <c r="G136" t="n">
+        <v>272.110763</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="n">
+        <v>163</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1</v>
+      </c>
+      <c r="D137" t="n">
+        <v>95.73699999999999</v>
+      </c>
+      <c r="E137" t="n">
+        <v>515.421154</v>
+      </c>
+      <c r="F137" t="n">
+        <v>102.253143</v>
+      </c>
+      <c r="G137" t="n">
+        <v>355.853507</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="n">
+        <v>157</v>
+      </c>
+      <c r="C138" t="n">
+        <v>1</v>
+      </c>
+      <c r="D138" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="E138" t="n">
+        <v>523.168088</v>
+      </c>
+      <c r="F138" t="n">
+        <v>44.652879</v>
+      </c>
+      <c r="G138" t="n">
+        <v>246.517635</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="n">
+        <v>54</v>
+      </c>
+      <c r="C139" t="n">
+        <v>1</v>
+      </c>
+      <c r="D139" t="n">
+        <v>100.57</v>
+      </c>
+      <c r="E139" t="n">
+        <v>524.812796</v>
+      </c>
+      <c r="F139" t="n">
+        <v>-21.877799</v>
+      </c>
+      <c r="G139" t="n">
+        <v>569.943456</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="n">
+        <v>100</v>
+      </c>
+      <c r="C140" t="n">
+        <v>1</v>
+      </c>
+      <c r="D140" t="n">
+        <v>101.66</v>
+      </c>
+      <c r="E140" t="n">
+        <v>436.052368</v>
+      </c>
+      <c r="F140" t="n">
+        <v>-293.232146</v>
+      </c>
+      <c r="G140" t="n">
+        <v>210.010429</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="n">
+        <v>108</v>
+      </c>
+      <c r="C141" t="n">
+        <v>1</v>
+      </c>
+      <c r="D141" t="n">
+        <v>103.68</v>
+      </c>
+      <c r="E141" t="n">
+        <v>525.1057089999999</v>
+      </c>
+      <c r="F141" t="n">
+        <v>-0.808161</v>
+      </c>
+      <c r="G141" t="n">
+        <v>150.599499</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="n">
+        <v>52</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1</v>
+      </c>
+      <c r="D142" t="n">
+        <v>103.81</v>
+      </c>
+      <c r="E142" t="n">
+        <v>524.133775</v>
+      </c>
+      <c r="F142" t="n">
+        <v>-34.324366</v>
+      </c>
+      <c r="G142" t="n">
+        <v>146.863806</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="n">
+        <v>17</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" t="n">
+        <v>106.44</v>
+      </c>
+      <c r="E143" t="n">
+        <v>510.524793</v>
+      </c>
+      <c r="F143" t="n">
+        <v>-125.599406</v>
+      </c>
+      <c r="G143" t="n">
+        <v>417.255998</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="n">
+        <v>19</v>
+      </c>
+      <c r="C144" t="n">
+        <v>1</v>
+      </c>
+      <c r="D144" t="n">
+        <v>119.73</v>
+      </c>
+      <c r="E144" t="n">
+        <v>32.459384</v>
+      </c>
+      <c r="F144" t="n">
+        <v>524.070703</v>
+      </c>
+      <c r="G144" t="n">
+        <v>366.405324</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="n">
+        <v>56</v>
+      </c>
+      <c r="C145" t="n">
+        <v>1</v>
+      </c>
+      <c r="D145" t="n">
+        <v>120.6</v>
+      </c>
+      <c r="E145" t="n">
+        <v>525.08602</v>
+      </c>
+      <c r="F145" t="n">
+        <v>-6.002297</v>
+      </c>
+      <c r="G145" t="n">
+        <v>287.243236</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="n">
+        <v>6</v>
+      </c>
+      <c r="C146" t="n">
+        <v>1</v>
+      </c>
+      <c r="D146" t="n">
+        <v>124.31</v>
+      </c>
+      <c r="E146" t="n">
+        <v>200.509079</v>
+      </c>
+      <c r="F146" t="n">
+        <v>-485.333149</v>
+      </c>
+      <c r="G146" t="n">
+        <v>218.576862</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="n">
+        <v>188</v>
+      </c>
+      <c r="C147" t="n">
+        <v>1</v>
+      </c>
+      <c r="D147" t="n">
+        <v>126.86</v>
+      </c>
+      <c r="E147" t="n">
+        <v>516.236969</v>
+      </c>
+      <c r="F147" t="n">
+        <v>96.677403</v>
+      </c>
+      <c r="G147" t="n">
+        <v>283.052442</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="n">
+        <v>178</v>
+      </c>
+      <c r="C148" t="n">
+        <v>1</v>
+      </c>
+      <c r="D148" t="n">
+        <v>129.28</v>
+      </c>
+      <c r="E148" t="n">
+        <v>459.889001</v>
+      </c>
+      <c r="F148" t="n">
+        <v>-253.840785999999</v>
+      </c>
+      <c r="G148" t="n">
+        <v>457.3549400000001</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="n">
+        <v>144</v>
+      </c>
+      <c r="C149" t="n">
+        <v>1</v>
+      </c>
+      <c r="D149" t="n">
+        <v>130.14</v>
+      </c>
+      <c r="E149" t="n">
+        <v>523.479812</v>
+      </c>
+      <c r="F149" t="n">
+        <v>-45.134814</v>
+      </c>
+      <c r="G149" t="n">
+        <v>474.756783</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="n">
+        <v>165</v>
+      </c>
+      <c r="C150" t="n">
+        <v>1</v>
+      </c>
+      <c r="D150" t="n">
+        <v>141.73</v>
+      </c>
+      <c r="E150" t="n">
+        <v>517.802501</v>
+      </c>
+      <c r="F150" t="n">
+        <v>88.16416</v>
+      </c>
+      <c r="G150" t="n">
+        <v>132.007989</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="n">
+        <v>93</v>
+      </c>
+      <c r="C151" t="n">
+        <v>1</v>
+      </c>
+      <c r="D151" t="n">
+        <v>157.97</v>
+      </c>
+      <c r="E151" t="n">
+        <v>524.93623</v>
+      </c>
+      <c r="F151" t="n">
+        <v>23.685552</v>
+      </c>
+      <c r="G151" t="n">
+        <v>424.227001</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="n">
+        <v>198</v>
+      </c>
+      <c r="C152" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" t="n">
+        <v>161.54</v>
+      </c>
+      <c r="E152" t="n">
+        <v>523.341638</v>
+      </c>
+      <c r="F152" t="n">
+        <v>-42.394107</v>
+      </c>
+      <c r="G152" t="n">
+        <v>441.229721</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="n">
+        <v>12</v>
+      </c>
+      <c r="C153" t="n">
+        <v>1</v>
+      </c>
+      <c r="D153" t="n">
+        <v>161.73</v>
+      </c>
+      <c r="E153" t="n">
+        <v>463.230442</v>
+      </c>
+      <c r="F153" t="n">
+        <v>-247.137327</v>
+      </c>
+      <c r="G153" t="n">
+        <v>598.506569</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="n">
+        <v>130</v>
+      </c>
+      <c r="C154" t="n">
+        <v>1</v>
+      </c>
+      <c r="D154" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="E154" t="n">
+        <v>446.55112</v>
+      </c>
+      <c r="F154" t="n">
+        <v>276.639092</v>
+      </c>
+      <c r="G154" t="n">
+        <v>416.713165</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="n">
+        <v>18</v>
+      </c>
+      <c r="C155" t="n">
+        <v>1</v>
+      </c>
+      <c r="D155" t="n">
+        <v>172.64</v>
+      </c>
+      <c r="E155" t="n">
+        <v>374.825509</v>
+      </c>
+      <c r="F155" t="n">
+        <v>367.822753</v>
+      </c>
+      <c r="G155" t="n">
+        <v>145.34321</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="n">
+        <v>59</v>
+      </c>
+      <c r="C156" t="n">
+        <v>1</v>
+      </c>
+      <c r="D156" t="n">
+        <v>179.84</v>
+      </c>
+      <c r="E156" t="n">
+        <v>440.64019</v>
+      </c>
+      <c r="F156" t="n">
+        <v>-285.575435</v>
+      </c>
+      <c r="G156" t="n">
+        <v>329.750019</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="n">
+        <v>128</v>
+      </c>
+      <c r="C157" t="n">
+        <v>1</v>
+      </c>
+      <c r="D157" t="n">
+        <v>186.87</v>
+      </c>
+      <c r="E157" t="n">
+        <v>503.871591</v>
+      </c>
+      <c r="F157" t="n">
+        <v>-147.963586</v>
+      </c>
+      <c r="G157" t="n">
+        <v>489.3968</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="n">
+        <v>55</v>
+      </c>
+      <c r="C158" t="n">
+        <v>1</v>
+      </c>
+      <c r="D158" t="n">
+        <v>188.67</v>
+      </c>
+      <c r="E158" t="n">
+        <v>511.0521480000001</v>
+      </c>
+      <c r="F158" t="n">
+        <v>-122.003348</v>
+      </c>
+      <c r="G158" t="n">
+        <v>122.088376</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="n">
+        <v>143</v>
+      </c>
+      <c r="C159" t="n">
+        <v>1</v>
+      </c>
+      <c r="D159" t="n">
+        <v>192.01</v>
+      </c>
+      <c r="E159" t="n">
+        <v>469.589246</v>
+      </c>
+      <c r="F159" t="n">
+        <v>-235.255741</v>
+      </c>
+      <c r="G159" t="n">
+        <v>285.443172</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="n">
+        <v>99</v>
+      </c>
+      <c r="C160" t="n">
+        <v>1</v>
+      </c>
+      <c r="D160" t="n">
+        <v>192.08</v>
+      </c>
+      <c r="E160" t="n">
+        <v>434.887508</v>
+      </c>
+      <c r="F160" t="n">
+        <v>294.839663</v>
+      </c>
+      <c r="G160" t="n">
+        <v>118.243656</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="n">
+        <v>171</v>
+      </c>
+      <c r="C161" t="n">
+        <v>1</v>
+      </c>
+      <c r="D161" t="n">
+        <v>214.49</v>
+      </c>
+      <c r="E161" t="n">
+        <v>519.211307</v>
+      </c>
+      <c r="F161" t="n">
+        <v>-77.90040399999999</v>
+      </c>
+      <c r="G161" t="n">
+        <v>549.8170660000001</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="n">
+        <v>10</v>
+      </c>
+      <c r="C162" t="n">
+        <v>1</v>
+      </c>
+      <c r="D162" t="n">
+        <v>219.73</v>
+      </c>
+      <c r="E162" t="n">
+        <v>397.50664</v>
+      </c>
+      <c r="F162" t="n">
+        <v>343.957741</v>
+      </c>
+      <c r="G162" t="n">
+        <v>220.415185</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="n">
+        <v>116</v>
+      </c>
+      <c r="C163" t="n">
+        <v>1</v>
+      </c>
+      <c r="D163" t="n">
+        <v>231.76</v>
+      </c>
+      <c r="E163" t="n">
+        <v>482.800103</v>
+      </c>
+      <c r="F163" t="n">
+        <v>-207.350104</v>
+      </c>
+      <c r="G163" t="n">
+        <v>535.069801</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="n">
+        <v>9</v>
+      </c>
+      <c r="C164" t="n">
+        <v>1</v>
+      </c>
+      <c r="D164" t="n">
+        <v>241.76</v>
+      </c>
+      <c r="E164" t="n">
+        <v>483.341559</v>
+      </c>
+      <c r="F164" t="n">
+        <v>206.390346</v>
+      </c>
+      <c r="G164" t="n">
+        <v>368.886707</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="n">
+        <v>66</v>
+      </c>
+      <c r="C165" t="n">
+        <v>1</v>
+      </c>
+      <c r="D165" t="n">
+        <v>275.68</v>
+      </c>
+      <c r="E165" t="n">
+        <v>406.444514</v>
+      </c>
+      <c r="F165" t="n">
+        <v>-332.697656</v>
+      </c>
+      <c r="G165" t="n">
+        <v>378.340129</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="n">
+        <v>83</v>
+      </c>
+      <c r="C166" t="n">
+        <v>1</v>
+      </c>
+      <c r="D166" t="n">
+        <v>286.57</v>
+      </c>
+      <c r="E166" t="n">
+        <v>493.068627</v>
+      </c>
+      <c r="F166" t="n">
+        <v>-181.007473</v>
+      </c>
+      <c r="G166" t="n">
+        <v>148.298139</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="n">
+        <v>5</v>
+      </c>
+      <c r="C167" t="n">
+        <v>1</v>
+      </c>
+      <c r="D167" t="n">
+        <v>301.61</v>
+      </c>
+      <c r="E167" t="n">
+        <v>425.775318</v>
+      </c>
+      <c r="F167" t="n">
+        <v>-308.269741</v>
+      </c>
+      <c r="G167" t="n">
+        <v>378.280952</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="n">
+        <v>35</v>
+      </c>
+      <c r="C168" t="n">
+        <v>1</v>
+      </c>
+      <c r="D168" t="n">
+        <v>313.38</v>
+      </c>
+      <c r="E168" t="n">
+        <v>495.948273</v>
+      </c>
+      <c r="F168" t="n">
+        <v>172.863842</v>
+      </c>
+      <c r="G168" t="n">
+        <v>417.033803</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="n">
+        <v>81</v>
+      </c>
+      <c r="C169" t="n">
+        <v>1</v>
+      </c>
+      <c r="D169" t="n">
+        <v>335.8</v>
+      </c>
+      <c r="E169" t="n">
+        <v>425.901429</v>
+      </c>
+      <c r="F169" t="n">
+        <v>-307.318302999999</v>
+      </c>
+      <c r="G169" t="n">
+        <v>496.710066</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="n">
+        <v>151</v>
+      </c>
+      <c r="C170" t="n">
+        <v>1</v>
+      </c>
+      <c r="D170" t="n">
+        <v>401.5</v>
+      </c>
+      <c r="E170" t="n">
+        <v>472.21133</v>
+      </c>
+      <c r="F170" t="n">
+        <v>230.423846</v>
+      </c>
+      <c r="G170" t="n">
+        <v>132.380917</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="n">
+        <v>140</v>
+      </c>
+      <c r="C171" t="n">
+        <v>1</v>
+      </c>
+      <c r="D171" t="n">
+        <v>443.77</v>
+      </c>
+      <c r="E171" t="n">
+        <v>518.787235</v>
+      </c>
+      <c r="F171" t="n">
+        <v>-82.286571</v>
+      </c>
+      <c r="G171" t="n">
+        <v>377.252186</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="n">
+        <v>21</v>
+      </c>
+      <c r="C172" t="n">
+        <v>1</v>
+      </c>
+      <c r="D172" t="n">
+        <v>539.8200000000001</v>
+      </c>
+      <c r="E172" t="n">
+        <v>474.995091</v>
+      </c>
+      <c r="F172" t="n">
+        <v>-224.763487</v>
+      </c>
+      <c r="G172" t="n">
+        <v>149.763753</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/np_detachment/np_sorted_file.xlsx
+++ b/np_detachment/np_sorted_file.xlsx
@@ -1,34 +1,52 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
   <fonts count="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +65,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -199,6 +150,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,6 +185,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -267,20 +220,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -402,4509 +351,4557 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H172"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="16.6640625" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" customWidth="1"/>
+    <col min="9" max="9" width="16.6640625" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" customWidth="1"/>
+    <col min="11" max="11" width="16.6640625" customWidth="1"/>
+    <col min="12" max="12" width="16.6640625" customWidth="1"/>
+    <col min="13" max="13" width="16.6640625" customWidth="1"/>
+    <col min="14" max="14" width="16.6640625" customWidth="1"/>
+    <col min="15" max="15" width="16.6640625" customWidth="1"/>
+    <col min="16" max="16" width="16.6640625" customWidth="1"/>
+    <col min="17" max="17" width="16.6640625" customWidth="1"/>
+    <col min="18" max="18" width="16.6640625" customWidth="1"/>
+    <col min="19" max="19" width="16.6640625" customWidth="1"/>
+    <col min="20" max="20" width="16.6640625" customWidth="1"/>
+    <col min="21" max="21" width="16.6640625" customWidth="1"/>
+    <col min="22" max="22" width="16.6640625" customWidth="1"/>
+    <col min="23" max="23" width="16.6640625" customWidth="1"/>
+    <col min="24" max="24" width="16.6640625" customWidth="1"/>
+    <col min="25" max="25" width="16.6640625" customWidth="1"/>
+    <col min="26" max="26" width="16.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>renumbered</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>run</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>fileNum</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>simulation time</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>lig_x</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>lig_y</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>lig_z</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Number of Bonds Left</t>
-        </is>
+      <c r="A1" t="str">
+        <v>renumbered</v>
+      </c>
+      <c r="B1" t="str">
+        <v>run</v>
+      </c>
+      <c r="C1" t="str">
+        <v>fileNum</v>
+      </c>
+      <c r="D1" t="str">
+        <v>simulation time</v>
+      </c>
+      <c r="E1" t="str">
+        <v>lig_x</v>
+      </c>
+      <c r="F1" t="str">
+        <v>lig_y</v>
+      </c>
+      <c r="G1" t="str">
+        <v>lig_z</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Number of Bonds Left</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="n">
+      <c r="A2" t="str">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
         <v>124</v>
       </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="C2" t="str">
+        <v>1</v>
+      </c>
+      <c r="D2" t="str">
         <v>0.065265</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="str">
         <v>523.310434</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" t="str">
         <v>-48.01272</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" t="str">
         <v>435.651627</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" t="str">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" t="str">
         <v>111</v>
       </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="C3" t="str">
+        <v>1</v>
+      </c>
+      <c r="D3" t="str">
         <v>0.089642</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="str">
         <v>451.1393019999999</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" t="str">
         <v>269.322061</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" t="str">
         <v>413.148644</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" t="str">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" t="str">
         <v>154</v>
       </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="C4" t="str">
+        <v>1</v>
+      </c>
+      <c r="D4" t="str">
         <v>0.4325699999999999</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="str">
         <v>476.575302</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" t="str">
         <v>-221.21812</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" t="str">
         <v>190.81415</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" t="str">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" t="str">
         <v>102</v>
       </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="n">
+      <c r="C5" t="str">
+        <v>1</v>
+      </c>
+      <c r="D5" t="str">
         <v>0.56933</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="str">
         <v>413.207441</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" t="str">
         <v>324.376283</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" t="str">
         <v>462.074933</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" t="str">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" t="str">
         <v>136</v>
       </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="C6" t="str">
+        <v>1</v>
+      </c>
+      <c r="D6" t="str">
         <v>0.67748</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="str">
         <v>474.359113</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" t="str">
         <v>225.681311</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" t="str">
         <v>182.672466</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" t="str">
         <v>6</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" t="str">
         <v>127</v>
       </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
+      <c r="C7" t="str">
+        <v>1</v>
+      </c>
+      <c r="D7" t="str">
         <v>1.0448</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="str">
         <v>521.801728</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" t="str">
         <v>60.40944200000001</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" t="str">
         <v>321.476931</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" t="str">
         <v>7</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" t="str">
         <v>31</v>
       </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="C8" t="str">
+        <v>1</v>
+      </c>
+      <c r="D8" t="str">
         <v>1.2789</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="str">
         <v>258.142471</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" t="str">
         <v>457.280632</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" t="str">
         <v>244.808561</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" t="str">
         <v>8</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" t="str">
         <v>103</v>
       </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="C9" t="str">
+        <v>1</v>
+      </c>
+      <c r="D9" t="str">
         <v>1.3573</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="str">
         <v>236.772067</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" t="str">
         <v>469.421912</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" t="str">
         <v>148.454015</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" t="str">
         <v>9</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" t="str">
         <v>86</v>
       </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="n">
+      <c r="C10" t="str">
+        <v>1</v>
+      </c>
+      <c r="D10" t="str">
         <v>2.195</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="str">
         <v>513.621204</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" t="str">
         <v>-109.098333</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" t="str">
         <v>317.024926</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" t="str">
         <v>10</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" t="str">
         <v>26</v>
       </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" t="n">
+      <c r="C11" t="str">
+        <v>1</v>
+      </c>
+      <c r="D11" t="str">
         <v>2.3144</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="str">
         <v>521.6795139999999</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" t="str">
         <v>62.747659</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" t="str">
         <v>239.312962</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" t="str">
         <v>11</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" t="str">
         <v>96</v>
       </c>
-      <c r="C12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" t="n">
+      <c r="C12" t="str">
+        <v>1</v>
+      </c>
+      <c r="D12" t="str">
         <v>2.3453</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="str">
         <v>510.594192</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" t="str">
         <v>-122.925855</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" t="str">
         <v>206.433301</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" t="str">
         <v>12</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" t="str">
         <v>106</v>
       </c>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" t="n">
+      <c r="C13" t="str">
+        <v>1</v>
+      </c>
+      <c r="D13" t="str">
         <v>2.56</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="str">
         <v>522.9976</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" t="str">
         <v>47.060479</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" t="str">
         <v>435.713979</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" t="str">
         <v>13</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" t="str">
         <v>150</v>
       </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="n">
+      <c r="C14" t="str">
+        <v>1</v>
+      </c>
+      <c r="D14" t="str">
         <v>2.6377</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="str">
         <v>508.787379</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" t="str">
         <v>129.595181</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" t="str">
         <v>304.480705</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" t="str">
         <v>14</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" t="str">
         <v>75</v>
       </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="n">
+      <c r="C15" t="str">
+        <v>1</v>
+      </c>
+      <c r="D15" t="str">
         <v>2.953</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="str">
         <v>501.638135</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" t="str">
         <v>156.409213</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" t="str">
         <v>434.439681</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" t="str">
         <v>15</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" t="str">
         <v>44</v>
       </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="n">
+      <c r="C16" t="str">
+        <v>1</v>
+      </c>
+      <c r="D16" t="str">
         <v>3.2146</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" t="str">
         <v>433.08091</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" t="str">
         <v>-298.539064</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" t="str">
         <v>371.876423</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" t="str">
         <v>16</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" t="str">
         <v>146</v>
       </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="n">
+      <c r="C17" t="str">
+        <v>1</v>
+      </c>
+      <c r="D17" t="str">
         <v>3.2322</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" t="str">
         <v>514.358103</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" t="str">
         <v>111.317294</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" t="str">
         <v>540.962005</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18" t="str">
         <v>17</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" t="str">
         <v>180</v>
       </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="n">
+      <c r="C18" t="str">
+        <v>1</v>
+      </c>
+      <c r="D18" t="str">
         <v>3.2837</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" t="str">
         <v>398.557273</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" t="str">
         <v>-341.855209</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" t="str">
         <v>433.604871</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
+      <c r="A19" t="str">
         <v>18</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" t="str">
         <v>134</v>
       </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
+      <c r="C19" t="str">
+        <v>1</v>
+      </c>
+      <c r="D19" t="str">
         <v>3.3575</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" t="str">
         <v>516.56197</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" t="str">
         <v>-96.687341</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" t="str">
         <v>179.587898</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
+      <c r="A20" t="str">
         <v>19</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" t="str">
         <v>192</v>
       </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
+      <c r="C20" t="str">
+        <v>1</v>
+      </c>
+      <c r="D20" t="str">
         <v>3.6892</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" t="str">
         <v>317.329868</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" t="str">
         <v>418.465283</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" t="str">
         <v>250.173135</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
+      <c r="A21" t="str">
         <v>20</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" t="str">
         <v>156</v>
       </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="n">
+      <c r="C21" t="str">
+        <v>1</v>
+      </c>
+      <c r="D21" t="str">
         <v>3.8394</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" t="str">
         <v>150.563358</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" t="str">
         <v>-503.520888999999</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" t="str">
         <v>449.207544</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
+      <c r="A22" t="str">
         <v>21</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" t="str">
         <v>77</v>
       </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="n">
+      <c r="C22" t="str">
+        <v>1</v>
+      </c>
+      <c r="D22" t="str">
         <v>4.1044</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" t="str">
         <v>503.731568</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" t="str">
         <v>-149.337218</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22" t="str">
         <v>269.153026</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
+      <c r="A23" t="str">
         <v>22</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" t="str">
         <v>42</v>
       </c>
-      <c r="C23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" t="n">
+      <c r="C23" t="str">
+        <v>1</v>
+      </c>
+      <c r="D23" t="str">
         <v>4.1386</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" t="str">
         <v>485.767559</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" t="str">
         <v>-199.290587999999</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23" t="str">
         <v>225.675298</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
+      <c r="A24" t="str">
         <v>23</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" t="str">
         <v>186</v>
       </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="n">
+      <c r="C24" t="str">
+        <v>1</v>
+      </c>
+      <c r="D24" t="str">
         <v>4.6799</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" t="str">
         <v>384.237281</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" t="str">
         <v>358.01037</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24" t="str">
         <v>460.239554</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
+      <c r="A25" t="str">
         <v>24</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" t="str">
         <v>79</v>
       </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="n">
+      <c r="C25" t="str">
+        <v>1</v>
+      </c>
+      <c r="D25" t="str">
         <v>4.9674</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" t="str">
         <v>454.7988360000001</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25" t="str">
         <v>-262.497362</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25" t="str">
         <v>271.258786</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
+      <c r="A26" t="str">
         <v>25</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" t="str">
         <v>164</v>
       </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="n">
+      <c r="C26" t="str">
+        <v>1</v>
+      </c>
+      <c r="D26" t="str">
         <v>5.3843</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" t="str">
         <v>-386.393872</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26" t="str">
         <v>-355.756493</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26" t="str">
         <v>314.036983</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H26" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
+      <c r="A27" t="str">
         <v>26</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" t="str">
         <v>97</v>
       </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="n">
+      <c r="C27" t="str">
+        <v>1</v>
+      </c>
+      <c r="D27" t="str">
         <v>5.5104</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" t="str">
         <v>444.413654</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27" t="str">
         <v>279.735369</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27" t="str">
         <v>207.403734</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H27" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
+      <c r="A28" t="str">
         <v>27</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" t="str">
         <v>24</v>
       </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" t="n">
+      <c r="C28" t="str">
+        <v>1</v>
+      </c>
+      <c r="D28" t="str">
         <v>6.2219</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" t="str">
         <v>513.226462</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28" t="str">
         <v>111.147953</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28" t="str">
         <v>275.547382</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H28" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
+      <c r="A29" t="str">
         <v>28</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" t="str">
         <v>53</v>
       </c>
-      <c r="C29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" t="n">
+      <c r="C29" t="str">
+        <v>1</v>
+      </c>
+      <c r="D29" t="str">
         <v>6.2412</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" t="str">
         <v>504.702413</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29" t="str">
         <v>145.232646</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29" t="str">
         <v>183.417255</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H29" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
+      <c r="A30" t="str">
         <v>29</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" t="str">
         <v>74</v>
       </c>
-      <c r="C30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" t="n">
+      <c r="C30" t="str">
+        <v>1</v>
+      </c>
+      <c r="D30" t="str">
         <v>6.2662</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" t="str">
         <v>521.197258</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30" t="str">
         <v>-66.026765</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30" t="str">
         <v>323.083445</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H30" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
+      <c r="A31" t="str">
         <v>30</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" t="str">
         <v>15</v>
       </c>
-      <c r="C31" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" t="n">
+      <c r="C31" t="str">
+        <v>1</v>
+      </c>
+      <c r="D31" t="str">
         <v>6.2969</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" t="str">
         <v>458.385548</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31" t="str">
         <v>256.202031</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G31" t="str">
         <v>152.864661</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H31" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
+      <c r="A32" t="str">
         <v>31</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" t="str">
         <v>65</v>
       </c>
-      <c r="C32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" t="n">
+      <c r="C32" t="str">
+        <v>1</v>
+      </c>
+      <c r="D32" t="str">
         <v>6.6816</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" t="str">
         <v>463.2744</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32" t="str">
         <v>-248.087048</v>
       </c>
-      <c r="G32" t="n">
+      <c r="G32" t="str">
         <v>213.045746</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H32" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
+      <c r="A33" t="str">
         <v>32</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" t="str">
         <v>7</v>
       </c>
-      <c r="C33" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" t="n">
+      <c r="C33" t="str">
+        <v>1</v>
+      </c>
+      <c r="D33" t="str">
         <v>7.1096</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" t="str">
         <v>509.799065</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33" t="str">
         <v>-125.949003</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G33" t="str">
         <v>388.125336</v>
       </c>
-      <c r="H33" t="n">
+      <c r="H33" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
+      <c r="A34" t="str">
         <v>33</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34" t="str">
         <v>61</v>
       </c>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" t="n">
+      <c r="C34" t="str">
+        <v>1</v>
+      </c>
+      <c r="D34" t="str">
         <v>7.1385</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" t="str">
         <v>484.017883</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34" t="str">
         <v>-204.612762</v>
       </c>
-      <c r="G34" t="n">
+      <c r="G34" t="str">
         <v>512.472573</v>
       </c>
-      <c r="H34" t="n">
+      <c r="H34" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
+      <c r="A35" t="str">
         <v>34</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35" t="str">
         <v>104</v>
       </c>
-      <c r="C35" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" t="n">
+      <c r="C35" t="str">
+        <v>1</v>
+      </c>
+      <c r="D35" t="str">
         <v>7.2446</v>
       </c>
-      <c r="E35" t="n">
-        <v>525.4323910000001</v>
-      </c>
-      <c r="F35" t="n">
+      <c r="E35" t="str">
+        <v>525.432391</v>
+      </c>
+      <c r="F35" t="str">
         <v>5.145014</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G35" t="str">
         <v>167.032385</v>
       </c>
-      <c r="H35" t="n">
+      <c r="H35" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
+      <c r="A36" t="str">
         <v>35</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" t="str">
         <v>131</v>
       </c>
-      <c r="C36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" t="n">
+      <c r="C36" t="str">
+        <v>1</v>
+      </c>
+      <c r="D36" t="str">
         <v>7.6738</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" t="str">
         <v>212.379884</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36" t="str">
         <v>481.245814</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G36" t="str">
         <v>222.546196</v>
       </c>
-      <c r="H36" t="n">
+      <c r="H36" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
+      <c r="A37" t="str">
         <v>36</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37" t="str">
         <v>172</v>
       </c>
-      <c r="C37" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" t="n">
+      <c r="C37" t="str">
+        <v>1</v>
+      </c>
+      <c r="D37" t="str">
         <v>7.6852</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" t="str">
         <v>461.1068570000001</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F37" t="str">
         <v>252.086435</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G37" t="str">
         <v>118.314463</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H37" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
+      <c r="A38" t="str">
         <v>37</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" t="str">
         <v>25</v>
       </c>
-      <c r="C38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" t="n">
+      <c r="C38" t="str">
+        <v>1</v>
+      </c>
+      <c r="D38" t="str">
         <v>7.8274</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" t="str">
         <v>437.052917</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38" t="str">
         <v>-291.361152</v>
       </c>
-      <c r="G38" t="n">
+      <c r="G38" t="str">
         <v>358.086972</v>
       </c>
-      <c r="H38" t="n">
+      <c r="H38" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
+      <c r="A39" t="str">
         <v>38</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" t="str">
         <v>197</v>
       </c>
-      <c r="C39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" t="n">
-        <v>8.460100000000001</v>
-      </c>
-      <c r="E39" t="n">
+      <c r="C39" t="str">
+        <v>1</v>
+      </c>
+      <c r="D39" t="str">
+        <v>8.4601</v>
+      </c>
+      <c r="E39" t="str">
         <v>470.139405</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39" t="str">
         <v>234.257399</v>
       </c>
-      <c r="G39" t="n">
+      <c r="G39" t="str">
         <v>377.901527</v>
       </c>
-      <c r="H39" t="n">
+      <c r="H39" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
+      <c r="A40" t="str">
         <v>39</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40" t="str">
         <v>121</v>
       </c>
-      <c r="C40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" t="n">
-        <v>8.581200000000001</v>
-      </c>
-      <c r="E40" t="n">
+      <c r="C40" t="str">
+        <v>1</v>
+      </c>
+      <c r="D40" t="str">
+        <v>8.5812</v>
+      </c>
+      <c r="E40" t="str">
         <v>521.558161</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40" t="str">
         <v>63.53105600000001</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G40" t="str">
         <v>355.492146</v>
       </c>
-      <c r="H40" t="n">
+      <c r="H40" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
+      <c r="A41" t="str">
         <v>40</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" t="str">
         <v>20</v>
       </c>
-      <c r="C41" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" t="n">
-        <v>9.017799999999999</v>
-      </c>
-      <c r="E41" t="n">
+      <c r="C41" t="str">
+        <v>1</v>
+      </c>
+      <c r="D41" t="str">
+        <v>9.0178</v>
+      </c>
+      <c r="E41" t="str">
         <v>513.1105299999999</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41" t="str">
         <v>-114.000135</v>
       </c>
-      <c r="G41" t="n">
+      <c r="G41" t="str">
         <v>208.596961</v>
       </c>
-      <c r="H41" t="n">
+      <c r="H41" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
+      <c r="A42" t="str">
         <v>41</v>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" t="str">
         <v>153</v>
       </c>
-      <c r="C42" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" t="n">
-        <v>9.354799999999999</v>
-      </c>
-      <c r="E42" t="n">
+      <c r="C42" t="str">
+        <v>1</v>
+      </c>
+      <c r="D42" t="str">
+        <v>9.3548</v>
+      </c>
+      <c r="E42" t="str">
         <v>506.3614519999999</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F42" t="str">
         <v>-140.285059</v>
       </c>
-      <c r="G42" t="n">
+      <c r="G42" t="str">
         <v>226.917937</v>
       </c>
-      <c r="H42" t="n">
+      <c r="H42" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
+      <c r="A43" t="str">
         <v>42</v>
       </c>
-      <c r="B43" t="n">
+      <c r="B43" t="str">
         <v>169</v>
       </c>
-      <c r="C43" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" t="n">
-        <v>9.775499999999999</v>
-      </c>
-      <c r="E43" t="n">
-        <v>525.1931039999999</v>
-      </c>
-      <c r="F43" t="n">
+      <c r="C43" t="str">
+        <v>1</v>
+      </c>
+      <c r="D43" t="str">
+        <v>9.7755</v>
+      </c>
+      <c r="E43" t="str">
+        <v>525.193104</v>
+      </c>
+      <c r="F43" t="str">
         <v>-13.044069</v>
       </c>
-      <c r="G43" t="n">
+      <c r="G43" t="str">
         <v>292.365262</v>
       </c>
-      <c r="H43" t="n">
+      <c r="H43" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
+      <c r="A44" t="str">
         <v>43</v>
       </c>
-      <c r="B44" t="n">
+      <c r="B44" t="str">
         <v>49</v>
       </c>
-      <c r="C44" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" t="n">
-        <v>9.805999999999999</v>
-      </c>
-      <c r="E44" t="n">
+      <c r="C44" t="str">
+        <v>1</v>
+      </c>
+      <c r="D44" t="str">
+        <v>9.806</v>
+      </c>
+      <c r="E44" t="str">
         <v>524.992111</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44" t="str">
         <v>-11.217683</v>
       </c>
-      <c r="G44" t="n">
+      <c r="G44" t="str">
         <v>467.701654</v>
       </c>
-      <c r="H44" t="n">
+      <c r="H44" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
+      <c r="A45" t="str">
         <v>44</v>
       </c>
-      <c r="B45" t="n">
+      <c r="B45" t="str">
         <v>37</v>
       </c>
-      <c r="C45" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" t="n">
+      <c r="C45" t="str">
+        <v>1</v>
+      </c>
+      <c r="D45" t="str">
         <v>10.149</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" t="str">
         <v>421.837417</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45" t="str">
         <v>-313.062689</v>
       </c>
-      <c r="G45" t="n">
+      <c r="G45" t="str">
         <v>221.963516</v>
       </c>
-      <c r="H45" t="n">
+      <c r="H45" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="n">
+      <c r="A46" t="str">
         <v>45</v>
       </c>
-      <c r="B46" t="n">
+      <c r="B46" t="str">
         <v>63</v>
       </c>
-      <c r="C46" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" t="n">
+      <c r="C46" t="str">
+        <v>1</v>
+      </c>
+      <c r="D46" t="str">
         <v>10.952</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46" t="str">
         <v>521.376576</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F46" t="str">
         <v>62.397933</v>
       </c>
-      <c r="G46" t="n">
+      <c r="G46" t="str">
         <v>343.534782</v>
       </c>
-      <c r="H46" t="n">
+      <c r="H46" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
+      <c r="A47" t="str">
         <v>46</v>
       </c>
-      <c r="B47" t="n">
+      <c r="B47" t="str">
         <v>190</v>
       </c>
-      <c r="C47" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" t="n">
+      <c r="C47" t="str">
+        <v>1</v>
+      </c>
+      <c r="D47" t="str">
         <v>11.14</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47" t="str">
         <v>523.5146589999999</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F47" t="str">
         <v>43.68411500000001</v>
       </c>
-      <c r="G47" t="n">
+      <c r="G47" t="str">
         <v>263.961486</v>
       </c>
-      <c r="H47" t="n">
+      <c r="H47" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
+      <c r="A48" t="str">
         <v>47</v>
       </c>
-      <c r="B48" t="n">
+      <c r="B48" t="str">
         <v>118</v>
       </c>
-      <c r="C48" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" t="n">
+      <c r="C48" t="str">
+        <v>1</v>
+      </c>
+      <c r="D48" t="str">
         <v>11.462</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48" t="str">
         <v>521.928559</v>
       </c>
-      <c r="F48" t="n">
+      <c r="F48" t="str">
         <v>-60.677347</v>
       </c>
-      <c r="G48" t="n">
+      <c r="G48" t="str">
         <v>165.335847</v>
       </c>
-      <c r="H48" t="n">
+      <c r="H48" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
+      <c r="A49" t="str">
         <v>48</v>
       </c>
-      <c r="B49" t="n">
+      <c r="B49" t="str">
         <v>90</v>
       </c>
-      <c r="C49" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" t="n">
+      <c r="C49" t="str">
+        <v>1</v>
+      </c>
+      <c r="D49" t="str">
         <v>12.032</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49" t="str">
         <v>470.639876</v>
       </c>
-      <c r="F49" t="n">
+      <c r="F49" t="str">
         <v>-232.859531</v>
       </c>
-      <c r="G49" t="n">
+      <c r="G49" t="str">
         <v>371.890682</v>
       </c>
-      <c r="H49" t="n">
+      <c r="H49" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
+      <c r="A50" t="str">
         <v>49</v>
       </c>
-      <c r="B50" t="n">
+      <c r="B50" t="str">
         <v>72</v>
       </c>
-      <c r="C50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" t="n">
+      <c r="C50" t="str">
+        <v>1</v>
+      </c>
+      <c r="D50" t="str">
         <v>12.515</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50" t="str">
         <v>490.407191</v>
       </c>
-      <c r="F50" t="n">
+      <c r="F50" t="str">
         <v>-189.169043</v>
       </c>
-      <c r="G50" t="n">
+      <c r="G50" t="str">
         <v>281.719915</v>
       </c>
-      <c r="H50" t="n">
+      <c r="H50" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
+      <c r="A51" t="str">
         <v>50</v>
       </c>
-      <c r="B51" t="n">
+      <c r="B51" t="str">
         <v>183</v>
       </c>
-      <c r="C51" t="n">
-        <v>1</v>
-      </c>
-      <c r="D51" t="n">
+      <c r="C51" t="str">
+        <v>1</v>
+      </c>
+      <c r="D51" t="str">
         <v>12.853</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51" t="str">
         <v>472.6667860000001</v>
       </c>
-      <c r="F51" t="n">
+      <c r="F51" t="str">
         <v>229.208428</v>
       </c>
-      <c r="G51" t="n">
+      <c r="G51" t="str">
         <v>795.390311</v>
       </c>
-      <c r="H51" t="n">
+      <c r="H51" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="n">
+      <c r="A52" t="str">
         <v>51</v>
       </c>
-      <c r="B52" t="n">
+      <c r="B52" t="str">
         <v>174</v>
       </c>
-      <c r="C52" t="n">
-        <v>1</v>
-      </c>
-      <c r="D52" t="n">
+      <c r="C52" t="str">
+        <v>1</v>
+      </c>
+      <c r="D52" t="str">
         <v>12.873</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E52" t="str">
         <v>519.8025389999999</v>
       </c>
-      <c r="F52" t="n">
-        <v>-74.81963499999991</v>
-      </c>
-      <c r="G52" t="n">
+      <c r="F52" t="str">
+        <v>-74.8196349999999</v>
+      </c>
+      <c r="G52" t="str">
         <v>412.719636</v>
       </c>
-      <c r="H52" t="n">
+      <c r="H52" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="n">
+      <c r="A53" t="str">
         <v>52</v>
       </c>
-      <c r="B53" t="n">
+      <c r="B53" t="str">
         <v>119</v>
       </c>
-      <c r="C53" t="n">
-        <v>1</v>
-      </c>
-      <c r="D53" t="n">
+      <c r="C53" t="str">
+        <v>1</v>
+      </c>
+      <c r="D53" t="str">
         <v>13.299</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E53" t="str">
         <v>521.704197</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F53" t="str">
         <v>-60.4934469999999</v>
       </c>
-      <c r="G53" t="n">
+      <c r="G53" t="str">
         <v>264.073917</v>
       </c>
-      <c r="H53" t="n">
+      <c r="H53" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="n">
+      <c r="A54" t="str">
         <v>53</v>
       </c>
-      <c r="B54" t="n">
+      <c r="B54" t="str">
         <v>27</v>
       </c>
-      <c r="C54" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" t="n">
+      <c r="C54" t="str">
+        <v>1</v>
+      </c>
+      <c r="D54" t="str">
         <v>13.399</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54" t="str">
         <v>514.624855</v>
       </c>
-      <c r="F54" t="n">
+      <c r="F54" t="str">
         <v>-104.99075</v>
       </c>
-      <c r="G54" t="n">
+      <c r="G54" t="str">
         <v>222.499188</v>
       </c>
-      <c r="H54" t="n">
+      <c r="H54" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="n">
+      <c r="A55" t="str">
         <v>54</v>
       </c>
-      <c r="B55" t="n">
+      <c r="B55" t="str">
         <v>80</v>
       </c>
-      <c r="C55" t="n">
-        <v>1</v>
-      </c>
-      <c r="D55" t="n">
+      <c r="C55" t="str">
+        <v>1</v>
+      </c>
+      <c r="D55" t="str">
         <v>13.49</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55" t="str">
         <v>513.2371860000001</v>
       </c>
-      <c r="F55" t="n">
+      <c r="F55" t="str">
         <v>-113.174575</v>
       </c>
-      <c r="G55" t="n">
+      <c r="G55" t="str">
         <v>388.342413</v>
       </c>
-      <c r="H55" t="n">
+      <c r="H55" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="n">
+      <c r="A56" t="str">
         <v>55</v>
       </c>
-      <c r="B56" t="n">
+      <c r="B56" t="str">
         <v>41</v>
       </c>
-      <c r="C56" t="n">
-        <v>1</v>
-      </c>
-      <c r="D56" t="n">
+      <c r="C56" t="str">
+        <v>1</v>
+      </c>
+      <c r="D56" t="str">
         <v>13.659</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56" t="str">
         <v>445.473613</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F56" t="str">
         <v>278.111524</v>
       </c>
-      <c r="G56" t="n">
+      <c r="G56" t="str">
         <v>334.249344</v>
       </c>
-      <c r="H56" t="n">
+      <c r="H56" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="n">
+      <c r="A57" t="str">
         <v>56</v>
       </c>
-      <c r="B57" t="n">
+      <c r="B57" t="str">
         <v>123</v>
       </c>
-      <c r="C57" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" t="n">
+      <c r="C57" t="str">
+        <v>1</v>
+      </c>
+      <c r="D57" t="str">
         <v>14.237</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57" t="str">
         <v>434.1942360000001</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F57" t="str">
         <v>297.024889</v>
       </c>
-      <c r="G57" t="n">
+      <c r="G57" t="str">
         <v>348.47855</v>
       </c>
-      <c r="H57" t="n">
+      <c r="H57" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="n">
+      <c r="A58" t="str">
         <v>57</v>
       </c>
-      <c r="B58" t="n">
+      <c r="B58" t="str">
         <v>196</v>
       </c>
-      <c r="C58" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" t="n">
+      <c r="C58" t="str">
+        <v>1</v>
+      </c>
+      <c r="D58" t="str">
         <v>14.281</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E58" t="str">
         <v>402.213988</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F58" t="str">
         <v>-337.522832</v>
       </c>
-      <c r="G58" t="n">
+      <c r="G58" t="str">
         <v>245.628355</v>
       </c>
-      <c r="H58" t="n">
+      <c r="H58" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="n">
+      <c r="A59" t="str">
         <v>58</v>
       </c>
-      <c r="B59" t="n">
+      <c r="B59" t="str">
         <v>84</v>
       </c>
-      <c r="C59" t="n">
-        <v>1</v>
-      </c>
-      <c r="D59" t="n">
+      <c r="C59" t="str">
+        <v>1</v>
+      </c>
+      <c r="D59" t="str">
         <v>14.467</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E59" t="str">
         <v>484.219855</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F59" t="str">
         <v>-203.386269</v>
       </c>
-      <c r="G59" t="n">
+      <c r="G59" t="str">
         <v>183.464893</v>
       </c>
-      <c r="H59" t="n">
+      <c r="H59" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="n">
+      <c r="A60" t="str">
         <v>59</v>
       </c>
-      <c r="B60" t="n">
+      <c r="B60" t="str">
         <v>57</v>
       </c>
-      <c r="C60" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" t="n">
+      <c r="C60" t="str">
+        <v>1</v>
+      </c>
+      <c r="D60" t="str">
         <v>14.748</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E60" t="str">
         <v>411.909092</v>
       </c>
-      <c r="F60" t="n">
+      <c r="F60" t="str">
         <v>325.801534</v>
       </c>
-      <c r="G60" t="n">
+      <c r="G60" t="str">
         <v>572.284947</v>
       </c>
-      <c r="H60" t="n">
+      <c r="H60" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="n">
+      <c r="A61" t="str">
         <v>60</v>
       </c>
-      <c r="B61" t="n">
+      <c r="B61" t="str">
         <v>135</v>
       </c>
-      <c r="C61" t="n">
-        <v>1</v>
-      </c>
-      <c r="D61" t="n">
+      <c r="C61" t="str">
+        <v>1</v>
+      </c>
+      <c r="D61" t="str">
         <v>15.369</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E61" t="str">
         <v>493.317967</v>
       </c>
-      <c r="F61" t="n">
+      <c r="F61" t="str">
         <v>-183.02835</v>
       </c>
-      <c r="G61" t="n">
+      <c r="G61" t="str">
         <v>322.586961</v>
       </c>
-      <c r="H61" t="n">
+      <c r="H61" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="n">
+      <c r="A62" t="str">
         <v>61</v>
       </c>
-      <c r="B62" t="n">
+      <c r="B62" t="str">
         <v>3</v>
       </c>
-      <c r="C62" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" t="n">
+      <c r="C62" t="str">
+        <v>1</v>
+      </c>
+      <c r="D62" t="str">
         <v>15.474</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62" t="str">
         <v>516.941601</v>
       </c>
-      <c r="F62" t="n">
+      <c r="F62" t="str">
         <v>-93.914238</v>
       </c>
-      <c r="G62" t="n">
+      <c r="G62" t="str">
         <v>395.190428</v>
       </c>
-      <c r="H62" t="n">
+      <c r="H62" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="n">
+      <c r="A63" t="str">
         <v>62</v>
       </c>
-      <c r="B63" t="n">
+      <c r="B63" t="str">
         <v>177</v>
       </c>
-      <c r="C63" t="n">
-        <v>1</v>
-      </c>
-      <c r="D63" t="n">
+      <c r="C63" t="str">
+        <v>1</v>
+      </c>
+      <c r="D63" t="str">
         <v>16.462</v>
       </c>
-      <c r="E63" t="n">
+      <c r="E63" t="str">
         <v>400.161105</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F63" t="str">
         <v>-342.144717</v>
       </c>
-      <c r="G63" t="n">
+      <c r="G63" t="str">
         <v>309.674022</v>
       </c>
-      <c r="H63" t="n">
+      <c r="H63" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="n">
+      <c r="A64" t="str">
         <v>63</v>
       </c>
-      <c r="B64" t="n">
+      <c r="B64" t="str">
         <v>92</v>
       </c>
-      <c r="C64" t="n">
-        <v>1</v>
-      </c>
-      <c r="D64" t="n">
+      <c r="C64" t="str">
+        <v>1</v>
+      </c>
+      <c r="D64" t="str">
         <v>16.809</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E64" t="str">
         <v>516.05261</v>
       </c>
-      <c r="F64" t="n">
+      <c r="F64" t="str">
         <v>97.274503</v>
       </c>
-      <c r="G64" t="n">
+      <c r="G64" t="str">
         <v>138.475118</v>
       </c>
-      <c r="H64" t="n">
+      <c r="H64" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="n">
+      <c r="A65" t="str">
         <v>64</v>
       </c>
-      <c r="B65" t="n">
+      <c r="B65" t="str">
         <v>82</v>
       </c>
-      <c r="C65" t="n">
-        <v>1</v>
-      </c>
-      <c r="D65" t="n">
+      <c r="C65" t="str">
+        <v>1</v>
+      </c>
+      <c r="D65" t="str">
         <v>17.44</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E65" t="str">
         <v>519.286962</v>
       </c>
-      <c r="F65" t="n">
-        <v>-77.27350300000001</v>
-      </c>
-      <c r="G65" t="n">
+      <c r="F65" t="str">
+        <v>-77.273503</v>
+      </c>
+      <c r="G65" t="str">
         <v>195.933672</v>
       </c>
-      <c r="H65" t="n">
+      <c r="H65" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="n">
+      <c r="A66" t="str">
         <v>65</v>
       </c>
-      <c r="B66" t="n">
+      <c r="B66" t="str">
         <v>43</v>
       </c>
-      <c r="C66" t="n">
-        <v>1</v>
-      </c>
-      <c r="D66" t="n">
+      <c r="C66" t="str">
+        <v>1</v>
+      </c>
+      <c r="D66" t="str">
         <v>17.512</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E66" t="str">
         <v>499.212332</v>
       </c>
-      <c r="F66" t="n">
+      <c r="F66" t="str">
         <v>162.891364</v>
       </c>
-      <c r="G66" t="n">
+      <c r="G66" t="str">
         <v>532.91022</v>
       </c>
-      <c r="H66" t="n">
+      <c r="H66" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="n">
+      <c r="A67" t="str">
         <v>66</v>
       </c>
-      <c r="B67" t="n">
+      <c r="B67" t="str">
         <v>147</v>
       </c>
-      <c r="C67" t="n">
-        <v>1</v>
-      </c>
-      <c r="D67" t="n">
+      <c r="C67" t="str">
+        <v>1</v>
+      </c>
+      <c r="D67" t="str">
         <v>17.515</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E67" t="str">
         <v>508.954354</v>
       </c>
-      <c r="F67" t="n">
+      <c r="F67" t="str">
         <v>-130.030677</v>
       </c>
-      <c r="G67" t="n">
+      <c r="G67" t="str">
         <v>227.272186</v>
       </c>
-      <c r="H67" t="n">
+      <c r="H67" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="n">
+      <c r="A68" t="str">
         <v>67</v>
       </c>
-      <c r="B68" t="n">
+      <c r="B68" t="str">
         <v>73</v>
       </c>
-      <c r="C68" t="n">
-        <v>1</v>
-      </c>
-      <c r="D68" t="n">
+      <c r="C68" t="str">
+        <v>1</v>
+      </c>
+      <c r="D68" t="str">
         <v>17.617</v>
       </c>
-      <c r="E68" t="n">
+      <c r="E68" t="str">
         <v>515.633728</v>
       </c>
-      <c r="F68" t="n">
+      <c r="F68" t="str">
         <v>-101.646453</v>
       </c>
-      <c r="G68" t="n">
+      <c r="G68" t="str">
         <v>312.008076</v>
       </c>
-      <c r="H68" t="n">
+      <c r="H68" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
+      <c r="A69" t="str">
         <v>68</v>
       </c>
-      <c r="B69" t="n">
+      <c r="B69" t="str">
         <v>8</v>
       </c>
-      <c r="C69" t="n">
-        <v>1</v>
-      </c>
-      <c r="D69" t="n">
+      <c r="C69" t="str">
+        <v>1</v>
+      </c>
+      <c r="D69" t="str">
         <v>17.931</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E69" t="str">
         <v>423.911585</v>
       </c>
-      <c r="F69" t="n">
+      <c r="F69" t="str">
         <v>-309.843288</v>
       </c>
-      <c r="G69" t="n">
+      <c r="G69" t="str">
         <v>277.804245</v>
       </c>
-      <c r="H69" t="n">
+      <c r="H69" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="n">
+      <c r="A70" t="str">
         <v>69</v>
       </c>
-      <c r="B70" t="n">
+      <c r="B70" t="str">
         <v>62</v>
       </c>
-      <c r="C70" t="n">
-        <v>1</v>
-      </c>
-      <c r="D70" t="n">
+      <c r="C70" t="str">
+        <v>1</v>
+      </c>
+      <c r="D70" t="str">
         <v>19.861</v>
       </c>
-      <c r="E70" t="n">
+      <c r="E70" t="str">
         <v>478.76</v>
       </c>
-      <c r="F70" t="n">
+      <c r="F70" t="str">
         <v>-217.081296</v>
       </c>
-      <c r="G70" t="n">
+      <c r="G70" t="str">
         <v>193.27419</v>
       </c>
-      <c r="H70" t="n">
+      <c r="H70" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="n">
+      <c r="A71" t="str">
         <v>70</v>
       </c>
-      <c r="B71" t="n">
+      <c r="B71" t="str">
         <v>161</v>
       </c>
-      <c r="C71" t="n">
-        <v>1</v>
-      </c>
-      <c r="D71" t="n">
+      <c r="C71" t="str">
+        <v>1</v>
+      </c>
+      <c r="D71" t="str">
         <v>19.924</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E71" t="str">
         <v>524.882845</v>
       </c>
-      <c r="F71" t="n">
+      <c r="F71" t="str">
         <v>29.940826</v>
       </c>
-      <c r="G71" t="n">
+      <c r="G71" t="str">
         <v>331.967323</v>
       </c>
-      <c r="H71" t="n">
+      <c r="H71" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="n">
+      <c r="A72" t="str">
         <v>71</v>
       </c>
-      <c r="B72" t="n">
+      <c r="B72" t="str">
         <v>120</v>
       </c>
-      <c r="C72" t="n">
-        <v>1</v>
-      </c>
-      <c r="D72" t="n">
+      <c r="C72" t="str">
+        <v>1</v>
+      </c>
+      <c r="D72" t="str">
         <v>20.102</v>
       </c>
-      <c r="E72" t="n">
+      <c r="E72" t="str">
         <v>487.8185610000001</v>
       </c>
-      <c r="F72" t="n">
+      <c r="F72" t="str">
         <v>195.889129</v>
       </c>
-      <c r="G72" t="n">
+      <c r="G72" t="str">
         <v>159.905217</v>
       </c>
-      <c r="H72" t="n">
+      <c r="H72" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="n">
+      <c r="A73" t="str">
         <v>72</v>
       </c>
-      <c r="B73" t="n">
+      <c r="B73" t="str">
         <v>60</v>
       </c>
-      <c r="C73" t="n">
-        <v>1</v>
-      </c>
-      <c r="D73" t="n">
+      <c r="C73" t="str">
+        <v>1</v>
+      </c>
+      <c r="D73" t="str">
         <v>20.973</v>
       </c>
-      <c r="E73" t="n">
+      <c r="E73" t="str">
         <v>302.581157</v>
       </c>
-      <c r="F73" t="n">
+      <c r="F73" t="str">
         <v>429.0842730000001</v>
       </c>
-      <c r="G73" t="n">
+      <c r="G73" t="str">
         <v>412.588087</v>
       </c>
-      <c r="H73" t="n">
+      <c r="H73" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="n">
+      <c r="A74" t="str">
         <v>73</v>
       </c>
-      <c r="B74" t="n">
+      <c r="B74" t="str">
         <v>112</v>
       </c>
-      <c r="C74" t="n">
-        <v>1</v>
-      </c>
-      <c r="D74" t="n">
+      <c r="C74" t="str">
+        <v>1</v>
+      </c>
+      <c r="D74" t="str">
         <v>21.044</v>
       </c>
-      <c r="E74" t="n">
+      <c r="E74" t="str">
         <v>502.517621</v>
       </c>
-      <c r="F74" t="n">
+      <c r="F74" t="str">
         <v>152.812783</v>
       </c>
-      <c r="G74" t="n">
+      <c r="G74" t="str">
         <v>253.54675</v>
       </c>
-      <c r="H74" t="n">
+      <c r="H74" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="n">
+      <c r="A75" t="str">
         <v>74</v>
       </c>
-      <c r="B75" t="n">
+      <c r="B75" t="str">
         <v>200</v>
       </c>
-      <c r="C75" t="n">
-        <v>1</v>
-      </c>
-      <c r="D75" t="n">
+      <c r="C75" t="str">
+        <v>1</v>
+      </c>
+      <c r="D75" t="str">
         <v>21.613</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E75" t="str">
         <v>459.534755</v>
       </c>
-      <c r="F75" t="n">
+      <c r="F75" t="str">
         <v>-254.020504</v>
       </c>
-      <c r="G75" t="n">
+      <c r="G75" t="str">
         <v>371.562006</v>
       </c>
-      <c r="H75" t="n">
+      <c r="H75" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="n">
+      <c r="A76" t="str">
         <v>75</v>
       </c>
-      <c r="B76" t="n">
+      <c r="B76" t="str">
         <v>107</v>
       </c>
-      <c r="C76" t="n">
-        <v>1</v>
-      </c>
-      <c r="D76" t="n">
+      <c r="C76" t="str">
+        <v>1</v>
+      </c>
+      <c r="D76" t="str">
         <v>22.394</v>
       </c>
-      <c r="E76" t="n">
+      <c r="E76" t="str">
         <v>525.378548</v>
       </c>
-      <c r="F76" t="n">
+      <c r="F76" t="str">
         <v>-14.628501</v>
       </c>
-      <c r="G76" t="n">
+      <c r="G76" t="str">
         <v>347.494411</v>
       </c>
-      <c r="H76" t="n">
+      <c r="H76" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="n">
+      <c r="A77" t="str">
         <v>76</v>
       </c>
-      <c r="B77" t="n">
+      <c r="B77" t="str">
         <v>152</v>
       </c>
-      <c r="C77" t="n">
-        <v>1</v>
-      </c>
-      <c r="D77" t="n">
+      <c r="C77" t="str">
+        <v>1</v>
+      </c>
+      <c r="D77" t="str">
         <v>22.415</v>
       </c>
-      <c r="E77" t="n">
+      <c r="E77" t="str">
         <v>440.176325</v>
       </c>
-      <c r="F77" t="n">
+      <c r="F77" t="str">
         <v>286.26591</v>
       </c>
-      <c r="G77" t="n">
+      <c r="G77" t="str">
         <v>381.414821</v>
       </c>
-      <c r="H77" t="n">
+      <c r="H77" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="n">
+      <c r="A78" t="str">
         <v>77</v>
       </c>
-      <c r="B78" t="n">
+      <c r="B78" t="str">
         <v>173</v>
       </c>
-      <c r="C78" t="n">
-        <v>1</v>
-      </c>
-      <c r="D78" t="n">
+      <c r="C78" t="str">
+        <v>1</v>
+      </c>
+      <c r="D78" t="str">
         <v>22.6</v>
       </c>
-      <c r="E78" t="n">
+      <c r="E78" t="str">
         <v>525.354319</v>
       </c>
-      <c r="F78" t="n">
+      <c r="F78" t="str">
         <v>7.971756</v>
       </c>
-      <c r="G78" t="n">
+      <c r="G78" t="str">
         <v>234.573331</v>
       </c>
-      <c r="H78" t="n">
+      <c r="H78" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="n">
+      <c r="A79" t="str">
         <v>78</v>
       </c>
-      <c r="B79" t="n">
+      <c r="B79" t="str">
         <v>138</v>
       </c>
-      <c r="C79" t="n">
-        <v>1</v>
-      </c>
-      <c r="D79" t="n">
+      <c r="C79" t="str">
+        <v>1</v>
+      </c>
+      <c r="D79" t="str">
         <v>22.997</v>
       </c>
-      <c r="E79" t="n">
+      <c r="E79" t="str">
         <v>509.235611</v>
       </c>
-      <c r="F79" t="n">
+      <c r="F79" t="str">
         <v>-130.821606</v>
       </c>
-      <c r="G79" t="n">
+      <c r="G79" t="str">
         <v>129.02494</v>
       </c>
-      <c r="H79" t="n">
+      <c r="H79" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="n">
+      <c r="A80" t="str">
         <v>79</v>
       </c>
-      <c r="B80" t="n">
+      <c r="B80" t="str">
         <v>148</v>
       </c>
-      <c r="C80" t="n">
-        <v>1</v>
-      </c>
-      <c r="D80" t="n">
+      <c r="C80" t="str">
+        <v>1</v>
+      </c>
+      <c r="D80" t="str">
         <v>23.485</v>
       </c>
-      <c r="E80" t="n">
+      <c r="E80" t="str">
         <v>512.058692</v>
       </c>
-      <c r="F80" t="n">
+      <c r="F80" t="str">
         <v>116.317893</v>
       </c>
-      <c r="G80" t="n">
+      <c r="G80" t="str">
         <v>142.875694</v>
       </c>
-      <c r="H80" t="n">
+      <c r="H80" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="n">
+      <c r="A81" t="str">
         <v>80</v>
       </c>
-      <c r="B81" t="n">
+      <c r="B81" t="str">
         <v>69</v>
       </c>
-      <c r="C81" t="n">
-        <v>1</v>
-      </c>
-      <c r="D81" t="n">
+      <c r="C81" t="str">
+        <v>1</v>
+      </c>
+      <c r="D81" t="str">
         <v>23.533</v>
       </c>
-      <c r="E81" t="n">
+      <c r="E81" t="str">
         <v>442.028229</v>
       </c>
-      <c r="F81" t="n">
+      <c r="F81" t="str">
         <v>-283.675071</v>
       </c>
-      <c r="G81" t="n">
+      <c r="G81" t="str">
         <v>196.50026</v>
       </c>
-      <c r="H81" t="n">
+      <c r="H81" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="n">
+      <c r="A82" t="str">
         <v>81</v>
       </c>
-      <c r="B82" t="n">
+      <c r="B82" t="str">
         <v>2</v>
       </c>
-      <c r="C82" t="n">
-        <v>1</v>
-      </c>
-      <c r="D82" t="n">
+      <c r="C82" t="str">
+        <v>1</v>
+      </c>
+      <c r="D82" t="str">
         <v>23.824</v>
       </c>
-      <c r="E82" t="n">
+      <c r="E82" t="str">
         <v>523.766795</v>
       </c>
-      <c r="F82" t="n">
+      <c r="F82" t="str">
         <v>42.921676</v>
       </c>
-      <c r="G82" t="n">
+      <c r="G82" t="str">
         <v>304.421742</v>
       </c>
-      <c r="H82" t="n">
+      <c r="H82" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="n">
+      <c r="A83" t="str">
         <v>82</v>
       </c>
-      <c r="B83" t="n">
+      <c r="B83" t="str">
         <v>33</v>
       </c>
-      <c r="C83" t="n">
-        <v>1</v>
-      </c>
-      <c r="D83" t="n">
+      <c r="C83" t="str">
+        <v>1</v>
+      </c>
+      <c r="D83" t="str">
         <v>23.86</v>
       </c>
-      <c r="E83" t="n">
+      <c r="E83" t="str">
         <v>474.578364</v>
       </c>
-      <c r="F83" t="n">
+      <c r="F83" t="str">
         <v>-225.237870999999</v>
       </c>
-      <c r="G83" t="n">
+      <c r="G83" t="str">
         <v>429.151945</v>
       </c>
-      <c r="H83" t="n">
+      <c r="H83" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="n">
+      <c r="A84" t="str">
         <v>83</v>
       </c>
-      <c r="B84" t="n">
+      <c r="B84" t="str">
         <v>160</v>
       </c>
-      <c r="C84" t="n">
-        <v>1</v>
-      </c>
-      <c r="D84" t="n">
+      <c r="C84" t="str">
+        <v>1</v>
+      </c>
+      <c r="D84" t="str">
         <v>25.84</v>
       </c>
-      <c r="E84" t="n">
-        <v>515.0161419999999</v>
-      </c>
-      <c r="F84" t="n">
+      <c r="E84" t="str">
+        <v>515.016142</v>
+      </c>
+      <c r="F84" t="str">
         <v>105.59326</v>
       </c>
-      <c r="G84" t="n">
+      <c r="G84" t="str">
         <v>175.939585</v>
       </c>
-      <c r="H84" t="n">
+      <c r="H84" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="n">
+      <c r="A85" t="str">
         <v>84</v>
       </c>
-      <c r="B85" t="n">
+      <c r="B85" t="str">
         <v>109</v>
       </c>
-      <c r="C85" t="n">
-        <v>1</v>
-      </c>
-      <c r="D85" t="n">
+      <c r="C85" t="str">
+        <v>1</v>
+      </c>
+      <c r="D85" t="str">
         <v>27.321</v>
       </c>
-      <c r="E85" t="n">
+      <c r="E85" t="str">
         <v>524.17246</v>
       </c>
-      <c r="F85" t="n">
+      <c r="F85" t="str">
         <v>30.47681</v>
       </c>
-      <c r="G85" t="n">
+      <c r="G85" t="str">
         <v>211.096634</v>
       </c>
-      <c r="H85" t="n">
+      <c r="H85" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="n">
+      <c r="A86" t="str">
         <v>85</v>
       </c>
-      <c r="B86" t="n">
+      <c r="B86" t="str">
         <v>39</v>
       </c>
-      <c r="C86" t="n">
-        <v>1</v>
-      </c>
-      <c r="D86" t="n">
+      <c r="C86" t="str">
+        <v>1</v>
+      </c>
+      <c r="D86" t="str">
         <v>27.762</v>
       </c>
-      <c r="E86" t="n">
+      <c r="E86" t="str">
         <v>495.503813</v>
       </c>
-      <c r="F86" t="n">
+      <c r="F86" t="str">
         <v>-174.775537</v>
       </c>
-      <c r="G86" t="n">
+      <c r="G86" t="str">
         <v>452.9287240000001</v>
       </c>
-      <c r="H86" t="n">
+      <c r="H86" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="n">
+      <c r="A87" t="str">
         <v>86</v>
       </c>
-      <c r="B87" t="n">
+      <c r="B87" t="str">
         <v>145</v>
       </c>
-      <c r="C87" t="n">
-        <v>1</v>
-      </c>
-      <c r="D87" t="n">
+      <c r="C87" t="str">
+        <v>1</v>
+      </c>
+      <c r="D87" t="str">
         <v>28.321</v>
       </c>
-      <c r="E87" t="n">
+      <c r="E87" t="str">
         <v>325.696537</v>
       </c>
-      <c r="F87" t="n">
+      <c r="F87" t="str">
         <v>412.178594</v>
       </c>
-      <c r="G87" t="n">
+      <c r="G87" t="str">
         <v>419.860359</v>
       </c>
-      <c r="H87" t="n">
+      <c r="H87" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="n">
+      <c r="A88" t="str">
         <v>87</v>
       </c>
-      <c r="B88" t="n">
+      <c r="B88" t="str">
         <v>94</v>
       </c>
-      <c r="C88" t="n">
-        <v>1</v>
-      </c>
-      <c r="D88" t="n">
+      <c r="C88" t="str">
+        <v>1</v>
+      </c>
+      <c r="D88" t="str">
         <v>29.622</v>
       </c>
-      <c r="E88" t="n">
+      <c r="E88" t="str">
         <v>524.334072</v>
       </c>
-      <c r="F88" t="n">
+      <c r="F88" t="str">
         <v>29.608008</v>
       </c>
-      <c r="G88" t="n">
+      <c r="G88" t="str">
         <v>416.266854</v>
       </c>
-      <c r="H88" t="n">
+      <c r="H88" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="n">
+      <c r="A89" t="str">
         <v>88</v>
       </c>
-      <c r="B89" t="n">
+      <c r="B89" t="str">
         <v>95</v>
       </c>
-      <c r="C89" t="n">
-        <v>1</v>
-      </c>
-      <c r="D89" t="n">
+      <c r="C89" t="str">
+        <v>1</v>
+      </c>
+      <c r="D89" t="str">
         <v>31.431</v>
       </c>
-      <c r="E89" t="n">
+      <c r="E89" t="str">
         <v>440.207404</v>
       </c>
-      <c r="F89" t="n">
+      <c r="F89" t="str">
         <v>-286.259953</v>
       </c>
-      <c r="G89" t="n">
+      <c r="G89" t="str">
         <v>514.469736</v>
       </c>
-      <c r="H89" t="n">
+      <c r="H89" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="n">
+      <c r="A90" t="str">
         <v>89</v>
       </c>
-      <c r="B90" t="n">
+      <c r="B90" t="str">
         <v>195</v>
       </c>
-      <c r="C90" t="n">
-        <v>1</v>
-      </c>
-      <c r="D90" t="n">
+      <c r="C90" t="str">
+        <v>1</v>
+      </c>
+      <c r="D90" t="str">
         <v>32.009</v>
       </c>
-      <c r="E90" t="n">
+      <c r="E90" t="str">
         <v>485.014777</v>
       </c>
-      <c r="F90" t="n">
+      <c r="F90" t="str">
         <v>-204.026574</v>
       </c>
-      <c r="G90" t="n">
+      <c r="G90" t="str">
         <v>201.548584</v>
       </c>
-      <c r="H90" t="n">
+      <c r="H90" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="n">
+      <c r="A91" t="str">
         <v>90</v>
       </c>
-      <c r="B91" t="n">
+      <c r="B91" t="str">
         <v>68</v>
       </c>
-      <c r="C91" t="n">
-        <v>1</v>
-      </c>
-      <c r="D91" t="n">
+      <c r="C91" t="str">
+        <v>1</v>
+      </c>
+      <c r="D91" t="str">
         <v>32.267</v>
       </c>
-      <c r="E91" t="n">
+      <c r="E91" t="str">
         <v>490.600139</v>
       </c>
-      <c r="F91" t="n">
+      <c r="F91" t="str">
         <v>-187.066714</v>
       </c>
-      <c r="G91" t="n">
+      <c r="G91" t="str">
         <v>124.237822</v>
       </c>
-      <c r="H91" t="n">
+      <c r="H91" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="n">
+      <c r="A92" t="str">
         <v>91</v>
       </c>
-      <c r="B92" t="n">
+      <c r="B92" t="str">
         <v>36</v>
       </c>
-      <c r="C92" t="n">
-        <v>1</v>
-      </c>
-      <c r="D92" t="n">
+      <c r="C92" t="str">
+        <v>1</v>
+      </c>
+      <c r="D92" t="str">
         <v>32.743</v>
       </c>
-      <c r="E92" t="n">
+      <c r="E92" t="str">
         <v>503.679352</v>
       </c>
-      <c r="F92" t="n">
+      <c r="F92" t="str">
         <v>-149.59656</v>
       </c>
-      <c r="G92" t="n">
+      <c r="G92" t="str">
         <v>173.001125</v>
       </c>
-      <c r="H92" t="n">
+      <c r="H92" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="n">
+      <c r="A93" t="str">
         <v>92</v>
       </c>
-      <c r="B93" t="n">
+      <c r="B93" t="str">
         <v>51</v>
       </c>
-      <c r="C93" t="n">
-        <v>1</v>
-      </c>
-      <c r="D93" t="n">
+      <c r="C93" t="str">
+        <v>1</v>
+      </c>
+      <c r="D93" t="str">
         <v>34.891</v>
       </c>
-      <c r="E93" t="n">
+      <c r="E93" t="str">
         <v>525.028067</v>
       </c>
-      <c r="F93" t="n">
+      <c r="F93" t="str">
         <v>13.537286</v>
       </c>
-      <c r="G93" t="n">
+      <c r="G93" t="str">
         <v>125.750821</v>
       </c>
-      <c r="H93" t="n">
+      <c r="H93" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="n">
+      <c r="A94" t="str">
         <v>93</v>
       </c>
-      <c r="B94" t="n">
+      <c r="B94" t="str">
         <v>78</v>
       </c>
-      <c r="C94" t="n">
-        <v>1</v>
-      </c>
-      <c r="D94" t="n">
+      <c r="C94" t="str">
+        <v>1</v>
+      </c>
+      <c r="D94" t="str">
         <v>35.217</v>
       </c>
-      <c r="E94" t="n">
+      <c r="E94" t="str">
         <v>347.826212</v>
       </c>
-      <c r="F94" t="n">
+      <c r="F94" t="str">
         <v>-393.954563</v>
       </c>
-      <c r="G94" t="n">
+      <c r="G94" t="str">
         <v>194.336163</v>
       </c>
-      <c r="H94" t="n">
+      <c r="H94" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="n">
+      <c r="A95" t="str">
         <v>94</v>
       </c>
-      <c r="B95" t="n">
+      <c r="B95" t="str">
         <v>182</v>
       </c>
-      <c r="C95" t="n">
-        <v>1</v>
-      </c>
-      <c r="D95" t="n">
+      <c r="C95" t="str">
+        <v>1</v>
+      </c>
+      <c r="D95" t="str">
         <v>35.555</v>
       </c>
-      <c r="E95" t="n">
+      <c r="E95" t="str">
         <v>401.068258</v>
       </c>
-      <c r="F95" t="n">
+      <c r="F95" t="str">
         <v>-339.435694</v>
       </c>
-      <c r="G95" t="n">
+      <c r="G95" t="str">
         <v>446.404175</v>
       </c>
-      <c r="H95" t="n">
+      <c r="H95" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="n">
+      <c r="A96" t="str">
         <v>95</v>
       </c>
-      <c r="B96" t="n">
+      <c r="B96" t="str">
         <v>193</v>
       </c>
-      <c r="C96" t="n">
-        <v>1</v>
-      </c>
-      <c r="D96" t="n">
+      <c r="C96" t="str">
+        <v>1</v>
+      </c>
+      <c r="D96" t="str">
         <v>35.94</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E96" t="str">
         <v>394.857591</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F96" t="str">
         <v>-346.127379</v>
       </c>
-      <c r="G96" t="n">
+      <c r="G96" t="str">
         <v>209.957931</v>
       </c>
-      <c r="H96" t="n">
+      <c r="H96" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="n">
+      <c r="A97" t="str">
         <v>96</v>
       </c>
-      <c r="B97" t="n">
+      <c r="B97" t="str">
         <v>141</v>
       </c>
-      <c r="C97" t="n">
-        <v>1</v>
-      </c>
-      <c r="D97" t="n">
+      <c r="C97" t="str">
+        <v>1</v>
+      </c>
+      <c r="D97" t="str">
         <v>36.443</v>
       </c>
-      <c r="E97" t="n">
+      <c r="E97" t="str">
         <v>494.845534</v>
       </c>
-      <c r="F97" t="n">
+      <c r="F97" t="str">
         <v>177.748731</v>
       </c>
-      <c r="G97" t="n">
+      <c r="G97" t="str">
         <v>403.308401</v>
       </c>
-      <c r="H97" t="n">
+      <c r="H97" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="n">
+      <c r="A98" t="str">
         <v>97</v>
       </c>
-      <c r="B98" t="n">
+      <c r="B98" t="str">
         <v>189</v>
       </c>
-      <c r="C98" t="n">
-        <v>1</v>
-      </c>
-      <c r="D98" t="n">
+      <c r="C98" t="str">
+        <v>1</v>
+      </c>
+      <c r="D98" t="str">
         <v>37</v>
       </c>
-      <c r="E98" t="n">
+      <c r="E98" t="str">
         <v>486.755603</v>
       </c>
-      <c r="F98" t="n">
+      <c r="F98" t="str">
         <v>197.047162</v>
       </c>
-      <c r="G98" t="n">
+      <c r="G98" t="str">
         <v>129.834842</v>
       </c>
-      <c r="H98" t="n">
+      <c r="H98" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="n">
+      <c r="A99" t="str">
         <v>98</v>
       </c>
-      <c r="B99" t="n">
+      <c r="B99" t="str">
         <v>133</v>
       </c>
-      <c r="C99" t="n">
-        <v>1</v>
-      </c>
-      <c r="D99" t="n">
+      <c r="C99" t="str">
+        <v>1</v>
+      </c>
+      <c r="D99" t="str">
         <v>37.363</v>
       </c>
-      <c r="E99" t="n">
+      <c r="E99" t="str">
         <v>522.9895309999999</v>
       </c>
-      <c r="F99" t="n">
+      <c r="F99" t="str">
         <v>47.352887</v>
       </c>
-      <c r="G99" t="n">
+      <c r="G99" t="str">
         <v>382.699873</v>
       </c>
-      <c r="H99" t="n">
+      <c r="H99" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="n">
+      <c r="A100" t="str">
         <v>99</v>
       </c>
-      <c r="B100" t="n">
+      <c r="B100" t="str">
         <v>162</v>
       </c>
-      <c r="C100" t="n">
-        <v>1</v>
-      </c>
-      <c r="D100" t="n">
+      <c r="C100" t="str">
+        <v>1</v>
+      </c>
+      <c r="D100" t="str">
         <v>37.436</v>
       </c>
-      <c r="E100" t="n">
+      <c r="E100" t="str">
         <v>-91.198198</v>
       </c>
-      <c r="F100" t="n">
+      <c r="F100" t="str">
         <v>517.151302</v>
       </c>
-      <c r="G100" t="n">
+      <c r="G100" t="str">
         <v>200.77912</v>
       </c>
-      <c r="H100" t="n">
+      <c r="H100" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="n">
+      <c r="A101" t="str">
         <v>100</v>
       </c>
-      <c r="B101" t="n">
+      <c r="B101" t="str">
         <v>168</v>
       </c>
-      <c r="C101" t="n">
-        <v>1</v>
-      </c>
-      <c r="D101" t="n">
+      <c r="C101" t="str">
+        <v>1</v>
+      </c>
+      <c r="D101" t="str">
         <v>37.712</v>
       </c>
-      <c r="E101" t="n">
+      <c r="E101" t="str">
         <v>495.844814</v>
       </c>
-      <c r="F101" t="n">
+      <c r="F101" t="str">
         <v>174.573038</v>
       </c>
-      <c r="G101" t="n">
+      <c r="G101" t="str">
         <v>188.236384</v>
       </c>
-      <c r="H101" t="n">
+      <c r="H101" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="n">
+      <c r="A102" t="str">
         <v>101</v>
       </c>
-      <c r="B102" t="n">
+      <c r="B102" t="str">
         <v>110</v>
       </c>
-      <c r="C102" t="n">
-        <v>1</v>
-      </c>
-      <c r="D102" t="n">
+      <c r="C102" t="str">
+        <v>1</v>
+      </c>
+      <c r="D102" t="str">
         <v>38.119</v>
       </c>
-      <c r="E102" t="n">
+      <c r="E102" t="str">
         <v>517.197235</v>
       </c>
-      <c r="F102" t="n">
-        <v>-90.69134099999999</v>
-      </c>
-      <c r="G102" t="n">
+      <c r="F102" t="str">
+        <v>-90.691341</v>
+      </c>
+      <c r="G102" t="str">
         <v>405.040641</v>
       </c>
-      <c r="H102" t="n">
+      <c r="H102" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="n">
+      <c r="A103" t="str">
         <v>102</v>
       </c>
-      <c r="B103" t="n">
+      <c r="B103" t="str">
         <v>125</v>
       </c>
-      <c r="C103" t="n">
-        <v>1</v>
-      </c>
-      <c r="D103" t="n">
+      <c r="C103" t="str">
+        <v>1</v>
+      </c>
+      <c r="D103" t="str">
         <v>38.754</v>
       </c>
-      <c r="E103" t="n">
+      <c r="E103" t="str">
         <v>477.824679</v>
       </c>
-      <c r="F103" t="n">
+      <c r="F103" t="str">
         <v>-218.038925</v>
       </c>
-      <c r="G103" t="n">
+      <c r="G103" t="str">
         <v>199.136188</v>
       </c>
-      <c r="H103" t="n">
+      <c r="H103" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="n">
+      <c r="A104" t="str">
         <v>103</v>
       </c>
-      <c r="B104" t="n">
+      <c r="B104" t="str">
         <v>11</v>
       </c>
-      <c r="C104" t="n">
-        <v>1</v>
-      </c>
-      <c r="D104" t="n">
+      <c r="C104" t="str">
+        <v>1</v>
+      </c>
+      <c r="D104" t="str">
         <v>38.819</v>
       </c>
-      <c r="E104" t="n">
+      <c r="E104" t="str">
         <v>465.289686</v>
       </c>
-      <c r="F104" t="n">
+      <c r="F104" t="str">
         <v>-244.559798</v>
       </c>
-      <c r="G104" t="n">
+      <c r="G104" t="str">
         <v>249.842634</v>
       </c>
-      <c r="H104" t="n">
+      <c r="H104" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="n">
+      <c r="A105" t="str">
         <v>104</v>
       </c>
-      <c r="B105" t="n">
+      <c r="B105" t="str">
         <v>175</v>
       </c>
-      <c r="C105" t="n">
-        <v>1</v>
-      </c>
-      <c r="D105" t="n">
+      <c r="C105" t="str">
+        <v>1</v>
+      </c>
+      <c r="D105" t="str">
         <v>42.662</v>
       </c>
-      <c r="E105" t="n">
+      <c r="E105" t="str">
         <v>407.4832</v>
       </c>
-      <c r="F105" t="n">
+      <c r="F105" t="str">
         <v>331.25226</v>
       </c>
-      <c r="G105" t="n">
+      <c r="G105" t="str">
         <v>400.753101</v>
       </c>
-      <c r="H105" t="n">
+      <c r="H105" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="n">
+      <c r="A106" t="str">
         <v>105</v>
       </c>
-      <c r="B106" t="n">
+      <c r="B106" t="str">
         <v>126</v>
       </c>
-      <c r="C106" t="n">
-        <v>1</v>
-      </c>
-      <c r="D106" t="n">
+      <c r="C106" t="str">
+        <v>1</v>
+      </c>
+      <c r="D106" t="str">
         <v>43.761</v>
       </c>
-      <c r="E106" t="n">
+      <c r="E106" t="str">
         <v>477.273224</v>
       </c>
-      <c r="F106" t="n">
+      <c r="F106" t="str">
         <v>218.82235</v>
       </c>
-      <c r="G106" t="n">
+      <c r="G106" t="str">
         <v>354.379565</v>
       </c>
-      <c r="H106" t="n">
+      <c r="H106" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="n">
+      <c r="A107" t="str">
         <v>106</v>
       </c>
-      <c r="B107" t="n">
+      <c r="B107" t="str">
         <v>16</v>
       </c>
-      <c r="C107" t="n">
-        <v>1</v>
-      </c>
-      <c r="D107" t="n">
+      <c r="C107" t="str">
+        <v>1</v>
+      </c>
+      <c r="D107" t="str">
         <v>44.01300000000001</v>
       </c>
-      <c r="E107" t="n">
+      <c r="E107" t="str">
         <v>343.395947</v>
       </c>
-      <c r="F107" t="n">
+      <c r="F107" t="str">
         <v>-398.172033</v>
       </c>
-      <c r="G107" t="n">
+      <c r="G107" t="str">
         <v>384.912526</v>
       </c>
-      <c r="H107" t="n">
+      <c r="H107" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="n">
+      <c r="A108" t="str">
         <v>107</v>
       </c>
-      <c r="B108" t="n">
+      <c r="B108" t="str">
         <v>122</v>
       </c>
-      <c r="C108" t="n">
-        <v>1</v>
-      </c>
-      <c r="D108" t="n">
+      <c r="C108" t="str">
+        <v>1</v>
+      </c>
+      <c r="D108" t="str">
         <v>44.03</v>
       </c>
-      <c r="E108" t="n">
+      <c r="E108" t="str">
         <v>309.374836</v>
       </c>
-      <c r="F108" t="n">
+      <c r="F108" t="str">
         <v>424.496287</v>
       </c>
-      <c r="G108" t="n">
+      <c r="G108" t="str">
         <v>362.22542</v>
       </c>
-      <c r="H108" t="n">
+      <c r="H108" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="n">
+      <c r="A109" t="str">
         <v>108</v>
       </c>
-      <c r="B109" t="n">
+      <c r="B109" t="str">
         <v>70</v>
       </c>
-      <c r="C109" t="n">
-        <v>1</v>
-      </c>
-      <c r="D109" t="n">
+      <c r="C109" t="str">
+        <v>1</v>
+      </c>
+      <c r="D109" t="str">
         <v>46.123</v>
       </c>
-      <c r="E109" t="n">
+      <c r="E109" t="str">
         <v>499.437328</v>
       </c>
-      <c r="F109" t="n">
+      <c r="F109" t="str">
         <v>163.676345</v>
       </c>
-      <c r="G109" t="n">
+      <c r="G109" t="str">
         <v>192.302188</v>
       </c>
-      <c r="H109" t="n">
+      <c r="H109" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="n">
+      <c r="A110" t="str">
         <v>109</v>
       </c>
-      <c r="B110" t="n">
+      <c r="B110" t="str">
         <v>22</v>
       </c>
-      <c r="C110" t="n">
-        <v>1</v>
-      </c>
-      <c r="D110" t="n">
+      <c r="C110" t="str">
+        <v>1</v>
+      </c>
+      <c r="D110" t="str">
         <v>46.287</v>
       </c>
-      <c r="E110" t="n">
+      <c r="E110" t="str">
         <v>466.375777</v>
       </c>
-      <c r="F110" t="n">
+      <c r="F110" t="str">
         <v>-241.312179</v>
       </c>
-      <c r="G110" t="n">
+      <c r="G110" t="str">
         <v>645.518868</v>
       </c>
-      <c r="H110" t="n">
+      <c r="H110" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="n">
+      <c r="A111" t="str">
         <v>110</v>
       </c>
-      <c r="B111" t="n">
+      <c r="B111" t="str">
         <v>167</v>
       </c>
-      <c r="C111" t="n">
-        <v>1</v>
-      </c>
-      <c r="D111" t="n">
+      <c r="C111" t="str">
+        <v>1</v>
+      </c>
+      <c r="D111" t="str">
         <v>48.326</v>
       </c>
-      <c r="E111" t="n">
+      <c r="E111" t="str">
         <v>520.270519</v>
       </c>
-      <c r="F111" t="n">
+      <c r="F111" t="str">
         <v>-70.890725</v>
       </c>
-      <c r="G111" t="n">
+      <c r="G111" t="str">
         <v>311.19369</v>
       </c>
-      <c r="H111" t="n">
+      <c r="H111" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="n">
+      <c r="A112" t="str">
         <v>111</v>
       </c>
-      <c r="B112" t="n">
+      <c r="B112" t="str">
         <v>67</v>
       </c>
-      <c r="C112" t="n">
-        <v>1</v>
-      </c>
-      <c r="D112" t="n">
+      <c r="C112" t="str">
+        <v>1</v>
+      </c>
+      <c r="D112" t="str">
         <v>50.04600000000001</v>
       </c>
-      <c r="E112" t="n">
+      <c r="E112" t="str">
         <v>472.102285</v>
       </c>
-      <c r="F112" t="n">
+      <c r="F112" t="str">
         <v>-231.547133999999</v>
       </c>
-      <c r="G112" t="n">
+      <c r="G112" t="str">
         <v>206.140714</v>
       </c>
-      <c r="H112" t="n">
+      <c r="H112" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="n">
+      <c r="A113" t="str">
         <v>112</v>
       </c>
-      <c r="B113" t="n">
+      <c r="B113" t="str">
         <v>48</v>
       </c>
-      <c r="C113" t="n">
-        <v>1</v>
-      </c>
-      <c r="D113" t="n">
+      <c r="C113" t="str">
+        <v>1</v>
+      </c>
+      <c r="D113" t="str">
         <v>52.269</v>
       </c>
-      <c r="E113" t="n">
+      <c r="E113" t="str">
         <v>524.217129</v>
       </c>
-      <c r="F113" t="n">
+      <c r="F113" t="str">
         <v>36.73970300000001</v>
       </c>
-      <c r="G113" t="n">
+      <c r="G113" t="str">
         <v>147.288848</v>
       </c>
-      <c r="H113" t="n">
+      <c r="H113" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="n">
+      <c r="A114" t="str">
         <v>113</v>
       </c>
-      <c r="B114" t="n">
+      <c r="B114" t="str">
         <v>85</v>
       </c>
-      <c r="C114" t="n">
-        <v>1</v>
-      </c>
-      <c r="D114" t="n">
+      <c r="C114" t="str">
+        <v>1</v>
+      </c>
+      <c r="D114" t="str">
         <v>54.044</v>
       </c>
-      <c r="E114" t="n">
+      <c r="E114" t="str">
         <v>521.390634</v>
       </c>
-      <c r="F114" t="n">
+      <c r="F114" t="str">
         <v>64.69929499999999</v>
       </c>
-      <c r="G114" t="n">
+      <c r="G114" t="str">
         <v>410.329548</v>
       </c>
-      <c r="H114" t="n">
+      <c r="H114" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="n">
+      <c r="A115" t="str">
         <v>114</v>
       </c>
-      <c r="B115" t="n">
+      <c r="B115" t="str">
         <v>4</v>
       </c>
-      <c r="C115" t="n">
-        <v>1</v>
-      </c>
-      <c r="D115" t="n">
+      <c r="C115" t="str">
+        <v>1</v>
+      </c>
+      <c r="D115" t="str">
         <v>55.497</v>
       </c>
-      <c r="E115" t="n">
+      <c r="E115" t="str">
         <v>514.465189</v>
       </c>
-      <c r="F115" t="n">
+      <c r="F115" t="str">
         <v>107.065661</v>
       </c>
-      <c r="G115" t="n">
+      <c r="G115" t="str">
         <v>296.810468</v>
       </c>
-      <c r="H115" t="n">
+      <c r="H115" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="n">
+      <c r="A116" t="str">
         <v>115</v>
       </c>
-      <c r="B116" t="n">
+      <c r="B116" t="str">
         <v>13</v>
       </c>
-      <c r="C116" t="n">
-        <v>1</v>
-      </c>
-      <c r="D116" t="n">
+      <c r="C116" t="str">
+        <v>1</v>
+      </c>
+      <c r="D116" t="str">
         <v>55.76</v>
       </c>
-      <c r="E116" t="n">
+      <c r="E116" t="str">
         <v>377.369477</v>
       </c>
-      <c r="F116" t="n">
+      <c r="F116" t="str">
         <v>-365.05683</v>
       </c>
-      <c r="G116" t="n">
+      <c r="G116" t="str">
         <v>316.389103</v>
       </c>
-      <c r="H116" t="n">
+      <c r="H116" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="n">
+      <c r="A117" t="str">
         <v>116</v>
       </c>
-      <c r="B117" t="n">
+      <c r="B117" t="str">
         <v>58</v>
       </c>
-      <c r="C117" t="n">
-        <v>1</v>
-      </c>
-      <c r="D117" t="n">
+      <c r="C117" t="str">
+        <v>1</v>
+      </c>
+      <c r="D117" t="str">
         <v>56.51</v>
       </c>
-      <c r="E117" t="n">
+      <c r="E117" t="str">
         <v>519.266557</v>
       </c>
-      <c r="F117" t="n">
+      <c r="F117" t="str">
         <v>80.228938</v>
       </c>
-      <c r="G117" t="n">
+      <c r="G117" t="str">
         <v>161.954713</v>
       </c>
-      <c r="H117" t="n">
+      <c r="H117" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="n">
+      <c r="A118" t="str">
         <v>117</v>
       </c>
-      <c r="B118" t="n">
+      <c r="B118" t="str">
         <v>45</v>
       </c>
-      <c r="C118" t="n">
-        <v>1</v>
-      </c>
-      <c r="D118" t="n">
+      <c r="C118" t="str">
+        <v>1</v>
+      </c>
+      <c r="D118" t="str">
         <v>57.555</v>
       </c>
-      <c r="E118" t="n">
+      <c r="E118" t="str">
         <v>517.170475</v>
       </c>
-      <c r="F118" t="n">
+      <c r="F118" t="str">
         <v>-92.498604</v>
       </c>
-      <c r="G118" t="n">
+      <c r="G118" t="str">
         <v>386.899372</v>
       </c>
-      <c r="H118" t="n">
+      <c r="H118" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="n">
+      <c r="A119" t="str">
         <v>118</v>
       </c>
-      <c r="B119" t="n">
+      <c r="B119" t="str">
         <v>46</v>
       </c>
-      <c r="C119" t="n">
-        <v>1</v>
-      </c>
-      <c r="D119" t="n">
+      <c r="C119" t="str">
+        <v>1</v>
+      </c>
+      <c r="D119" t="str">
         <v>58.233</v>
       </c>
-      <c r="E119" t="n">
+      <c r="E119" t="str">
         <v>217.527593</v>
       </c>
-      <c r="F119" t="n">
+      <c r="F119" t="str">
         <v>-477.846117</v>
       </c>
-      <c r="G119" t="n">
+      <c r="G119" t="str">
         <v>324.272967</v>
       </c>
-      <c r="H119" t="n">
+      <c r="H119" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="n">
+      <c r="A120" t="str">
         <v>119</v>
       </c>
-      <c r="B120" t="n">
+      <c r="B120" t="str">
         <v>184</v>
       </c>
-      <c r="C120" t="n">
-        <v>1</v>
-      </c>
-      <c r="D120" t="n">
+      <c r="C120" t="str">
+        <v>1</v>
+      </c>
+      <c r="D120" t="str">
         <v>61.681</v>
       </c>
-      <c r="E120" t="n">
+      <c r="E120" t="str">
         <v>494.407887</v>
       </c>
-      <c r="F120" t="n">
+      <c r="F120" t="str">
         <v>-181.361369</v>
       </c>
-      <c r="G120" t="n">
+      <c r="G120" t="str">
         <v>237.742519</v>
       </c>
-      <c r="H120" t="n">
+      <c r="H120" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="n">
+      <c r="A121" t="str">
         <v>120</v>
       </c>
-      <c r="B121" t="n">
+      <c r="B121" t="str">
         <v>91</v>
       </c>
-      <c r="C121" t="n">
-        <v>1</v>
-      </c>
-      <c r="D121" t="n">
+      <c r="C121" t="str">
+        <v>1</v>
+      </c>
+      <c r="D121" t="str">
         <v>62.122</v>
       </c>
-      <c r="E121" t="n">
-        <v>525.0571660000001</v>
-      </c>
-      <c r="F121" t="n">
+      <c r="E121" t="str">
+        <v>525.057166</v>
+      </c>
+      <c r="F121" t="str">
         <v>-15.876593</v>
       </c>
-      <c r="G121" t="n">
+      <c r="G121" t="str">
         <v>140.464731</v>
       </c>
-      <c r="H121" t="n">
+      <c r="H121" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="n">
+      <c r="A122" t="str">
         <v>121</v>
       </c>
-      <c r="B122" t="n">
+      <c r="B122" t="str">
         <v>149</v>
       </c>
-      <c r="C122" t="n">
-        <v>1</v>
-      </c>
-      <c r="D122" t="n">
+      <c r="C122" t="str">
+        <v>1</v>
+      </c>
+      <c r="D122" t="str">
         <v>65.292</v>
       </c>
-      <c r="E122" t="n">
+      <c r="E122" t="str">
         <v>497.650993</v>
       </c>
-      <c r="F122" t="n">
+      <c r="F122" t="str">
         <v>168.530653</v>
       </c>
-      <c r="G122" t="n">
+      <c r="G122" t="str">
         <v>322.609964</v>
       </c>
-      <c r="H122" t="n">
+      <c r="H122" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="n">
+      <c r="A123" t="str">
         <v>122</v>
       </c>
-      <c r="B123" t="n">
+      <c r="B123" t="str">
         <v>187</v>
       </c>
-      <c r="C123" t="n">
-        <v>1</v>
-      </c>
-      <c r="D123" t="n">
-        <v>67.36799999999999</v>
-      </c>
-      <c r="E123" t="n">
+      <c r="C123" t="str">
+        <v>1</v>
+      </c>
+      <c r="D123" t="str">
+        <v>67.368</v>
+      </c>
+      <c r="E123" t="str">
         <v>463.193433</v>
       </c>
-      <c r="F123" t="n">
+      <c r="F123" t="str">
         <v>-247.740568</v>
       </c>
-      <c r="G123" t="n">
+      <c r="G123" t="str">
         <v>130.524294</v>
       </c>
-      <c r="H123" t="n">
+      <c r="H123" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="n">
+      <c r="A124" t="str">
         <v>123</v>
       </c>
-      <c r="B124" t="n">
+      <c r="B124" t="str">
         <v>142</v>
       </c>
-      <c r="C124" t="n">
-        <v>1</v>
-      </c>
-      <c r="D124" t="n">
-        <v>70.26300000000001</v>
-      </c>
-      <c r="E124" t="n">
+      <c r="C124" t="str">
+        <v>1</v>
+      </c>
+      <c r="D124" t="str">
+        <v>70.263</v>
+      </c>
+      <c r="E124" t="str">
         <v>476.099489</v>
       </c>
-      <c r="F124" t="n">
+      <c r="F124" t="str">
         <v>222.083699</v>
       </c>
-      <c r="G124" t="n">
+      <c r="G124" t="str">
         <v>407.418919</v>
       </c>
-      <c r="H124" t="n">
+      <c r="H124" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="n">
+      <c r="A125" t="str">
         <v>124</v>
       </c>
-      <c r="B125" t="n">
+      <c r="B125" t="str">
         <v>159</v>
       </c>
-      <c r="C125" t="n">
-        <v>1</v>
-      </c>
-      <c r="D125" t="n">
+      <c r="C125" t="str">
+        <v>1</v>
+      </c>
+      <c r="D125" t="str">
         <v>71.048</v>
       </c>
-      <c r="E125" t="n">
+      <c r="E125" t="str">
         <v>501.77071</v>
       </c>
-      <c r="F125" t="n">
+      <c r="F125" t="str">
         <v>-155.285239</v>
       </c>
-      <c r="G125" t="n">
+      <c r="G125" t="str">
         <v>145.867526</v>
       </c>
-      <c r="H125" t="n">
+      <c r="H125" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="n">
+      <c r="A126" t="str">
         <v>125</v>
       </c>
-      <c r="B126" t="n">
+      <c r="B126" t="str">
         <v>89</v>
       </c>
-      <c r="C126" t="n">
-        <v>1</v>
-      </c>
-      <c r="D126" t="n">
+      <c r="C126" t="str">
+        <v>1</v>
+      </c>
+      <c r="D126" t="str">
         <v>72.896</v>
       </c>
-      <c r="E126" t="n">
+      <c r="E126" t="str">
         <v>506.106032</v>
       </c>
-      <c r="F126" t="n">
+      <c r="F126" t="str">
         <v>-141.273875</v>
       </c>
-      <c r="G126" t="n">
+      <c r="G126" t="str">
         <v>568.168749</v>
       </c>
-      <c r="H126" t="n">
+      <c r="H126" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="n">
+      <c r="A127" t="str">
         <v>126</v>
       </c>
-      <c r="B127" t="n">
+      <c r="B127" t="str">
         <v>101</v>
       </c>
-      <c r="C127" t="n">
-        <v>1</v>
-      </c>
-      <c r="D127" t="n">
+      <c r="C127" t="str">
+        <v>1</v>
+      </c>
+      <c r="D127" t="str">
         <v>75.498</v>
       </c>
-      <c r="E127" t="n">
+      <c r="E127" t="str">
         <v>375.795788</v>
       </c>
-      <c r="F127" t="n">
+      <c r="F127" t="str">
         <v>-366.85854</v>
       </c>
-      <c r="G127" t="n">
+      <c r="G127" t="str">
         <v>143.065112</v>
       </c>
-      <c r="H127" t="n">
+      <c r="H127" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="n">
+      <c r="A128" t="str">
         <v>127</v>
       </c>
-      <c r="B128" t="n">
+      <c r="B128" t="str">
         <v>98</v>
       </c>
-      <c r="C128" t="n">
-        <v>1</v>
-      </c>
-      <c r="D128" t="n">
-        <v>78.45699999999999</v>
-      </c>
-      <c r="E128" t="n">
+      <c r="C128" t="str">
+        <v>1</v>
+      </c>
+      <c r="D128" t="str">
+        <v>78.457</v>
+      </c>
+      <c r="E128" t="str">
         <v>316.434008</v>
       </c>
-      <c r="F128" t="n">
+      <c r="F128" t="str">
         <v>419.13871</v>
       </c>
-      <c r="G128" t="n">
+      <c r="G128" t="str">
         <v>392.059615</v>
       </c>
-      <c r="H128" t="n">
+      <c r="H128" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="n">
+      <c r="A129" t="str">
         <v>128</v>
       </c>
-      <c r="B129" t="n">
+      <c r="B129" t="str">
         <v>64</v>
       </c>
-      <c r="C129" t="n">
-        <v>1</v>
-      </c>
-      <c r="D129" t="n">
+      <c r="C129" t="str">
+        <v>1</v>
+      </c>
+      <c r="D129" t="str">
         <v>78.99600000000001</v>
       </c>
-      <c r="E129" t="n">
+      <c r="E129" t="str">
         <v>518.521975</v>
       </c>
-      <c r="F129" t="n">
+      <c r="F129" t="str">
         <v>-83.601158</v>
       </c>
-      <c r="G129" t="n">
+      <c r="G129" t="str">
         <v>229.236567</v>
       </c>
-      <c r="H129" t="n">
+      <c r="H129" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="n">
+      <c r="A130" t="str">
         <v>129</v>
       </c>
-      <c r="B130" t="n">
+      <c r="B130" t="str">
         <v>117</v>
       </c>
-      <c r="C130" t="n">
-        <v>1</v>
-      </c>
-      <c r="D130" t="n">
+      <c r="C130" t="str">
+        <v>1</v>
+      </c>
+      <c r="D130" t="str">
         <v>80.492</v>
       </c>
-      <c r="E130" t="n">
+      <c r="E130" t="str">
         <v>385.683075</v>
       </c>
-      <c r="F130" t="n">
+      <c r="F130" t="str">
         <v>-357.530107</v>
       </c>
-      <c r="G130" t="n">
+      <c r="G130" t="str">
         <v>793.2176450000001</v>
       </c>
-      <c r="H130" t="n">
+      <c r="H130" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="n">
+      <c r="A131" t="str">
         <v>130</v>
       </c>
-      <c r="B131" t="n">
+      <c r="B131" t="str">
         <v>23</v>
       </c>
-      <c r="C131" t="n">
-        <v>1</v>
-      </c>
-      <c r="D131" t="n">
+      <c r="C131" t="str">
+        <v>1</v>
+      </c>
+      <c r="D131" t="str">
         <v>82.947</v>
       </c>
-      <c r="E131" t="n">
+      <c r="E131" t="str">
         <v>490.582685</v>
       </c>
-      <c r="F131" t="n">
+      <c r="F131" t="str">
         <v>-189.328332</v>
       </c>
-      <c r="G131" t="n">
+      <c r="G131" t="str">
         <v>508.895364</v>
       </c>
-      <c r="H131" t="n">
+      <c r="H131" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="n">
+      <c r="A132" t="str">
         <v>131</v>
       </c>
-      <c r="B132" t="n">
+      <c r="B132" t="str">
         <v>32</v>
       </c>
-      <c r="C132" t="n">
-        <v>1</v>
-      </c>
-      <c r="D132" t="n">
-        <v>88.00700000000001</v>
-      </c>
-      <c r="E132" t="n">
+      <c r="C132" t="str">
+        <v>1</v>
+      </c>
+      <c r="D132" t="str">
+        <v>88.007</v>
+      </c>
+      <c r="E132" t="str">
         <v>525.3268929999999</v>
       </c>
-      <c r="F132" t="n">
+      <c r="F132" t="str">
         <v>-0.5021</v>
       </c>
-      <c r="G132" t="n">
+      <c r="G132" t="str">
         <v>145.979109</v>
       </c>
-      <c r="H132" t="n">
+      <c r="H132" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="n">
+      <c r="A133" t="str">
         <v>132</v>
       </c>
-      <c r="B133" t="n">
+      <c r="B133" t="str">
         <v>191</v>
       </c>
-      <c r="C133" t="n">
-        <v>1</v>
-      </c>
-      <c r="D133" t="n">
+      <c r="C133" t="str">
+        <v>1</v>
+      </c>
+      <c r="D133" t="str">
         <v>89.616</v>
       </c>
-      <c r="E133" t="n">
+      <c r="E133" t="str">
         <v>396.575342</v>
       </c>
-      <c r="F133" t="n">
+      <c r="F133" t="str">
         <v>-344.249624</v>
       </c>
-      <c r="G133" t="n">
+      <c r="G133" t="str">
         <v>289.129589</v>
       </c>
-      <c r="H133" t="n">
+      <c r="H133" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="n">
+      <c r="A134" t="str">
         <v>133</v>
       </c>
-      <c r="B134" t="n">
+      <c r="B134" t="str">
         <v>129</v>
       </c>
-      <c r="C134" t="n">
-        <v>1</v>
-      </c>
-      <c r="D134" t="n">
+      <c r="C134" t="str">
+        <v>1</v>
+      </c>
+      <c r="D134" t="str">
         <v>89.816</v>
       </c>
-      <c r="E134" t="n">
+      <c r="E134" t="str">
         <v>496.303349</v>
       </c>
-      <c r="F134" t="n">
+      <c r="F134" t="str">
         <v>-171.660968</v>
       </c>
-      <c r="G134" t="n">
+      <c r="G134" t="str">
         <v>647.060288</v>
       </c>
-      <c r="H134" t="n">
+      <c r="H134" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="n">
+      <c r="A135" t="str">
         <v>134</v>
       </c>
-      <c r="B135" t="n">
+      <c r="B135" t="str">
         <v>88</v>
       </c>
-      <c r="C135" t="n">
-        <v>1</v>
-      </c>
-      <c r="D135" t="n">
+      <c r="C135" t="str">
+        <v>1</v>
+      </c>
+      <c r="D135" t="str">
         <v>91.003</v>
       </c>
-      <c r="E135" t="n">
+      <c r="E135" t="str">
         <v>524.245075</v>
       </c>
-      <c r="F135" t="n">
+      <c r="F135" t="str">
         <v>-32.112013</v>
       </c>
-      <c r="G135" t="n">
+      <c r="G135" t="str">
         <v>229.999342</v>
       </c>
-      <c r="H135" t="n">
+      <c r="H135" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="n">
+      <c r="A136" t="str">
         <v>135</v>
       </c>
-      <c r="B136" t="n">
+      <c r="B136" t="str">
         <v>28</v>
       </c>
-      <c r="C136" t="n">
-        <v>1</v>
-      </c>
-      <c r="D136" t="n">
+      <c r="C136" t="str">
+        <v>1</v>
+      </c>
+      <c r="D136" t="str">
         <v>91.291</v>
       </c>
-      <c r="E136" t="n">
+      <c r="E136" t="str">
         <v>503.654163</v>
       </c>
-      <c r="F136" t="n">
+      <c r="F136" t="str">
         <v>-148.624672</v>
       </c>
-      <c r="G136" t="n">
+      <c r="G136" t="str">
         <v>272.110763</v>
       </c>
-      <c r="H136" t="n">
+      <c r="H136" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="n">
+      <c r="A137" t="str">
         <v>136</v>
       </c>
-      <c r="B137" t="n">
+      <c r="B137" t="str">
         <v>163</v>
       </c>
-      <c r="C137" t="n">
-        <v>1</v>
-      </c>
-      <c r="D137" t="n">
-        <v>95.73699999999999</v>
-      </c>
-      <c r="E137" t="n">
+      <c r="C137" t="str">
+        <v>1</v>
+      </c>
+      <c r="D137" t="str">
+        <v>95.737</v>
+      </c>
+      <c r="E137" t="str">
         <v>515.421154</v>
       </c>
-      <c r="F137" t="n">
+      <c r="F137" t="str">
         <v>102.253143</v>
       </c>
-      <c r="G137" t="n">
+      <c r="G137" t="str">
         <v>355.853507</v>
       </c>
-      <c r="H137" t="n">
+      <c r="H137" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="n">
+      <c r="A138" t="str">
         <v>137</v>
       </c>
-      <c r="B138" t="n">
+      <c r="B138" t="str">
         <v>157</v>
       </c>
-      <c r="C138" t="n">
-        <v>1</v>
-      </c>
-      <c r="D138" t="n">
+      <c r="C138" t="str">
+        <v>1</v>
+      </c>
+      <c r="D138" t="str">
         <v>100.09</v>
       </c>
-      <c r="E138" t="n">
+      <c r="E138" t="str">
         <v>523.168088</v>
       </c>
-      <c r="F138" t="n">
+      <c r="F138" t="str">
         <v>44.652879</v>
       </c>
-      <c r="G138" t="n">
+      <c r="G138" t="str">
         <v>246.517635</v>
       </c>
-      <c r="H138" t="n">
+      <c r="H138" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="n">
+      <c r="A139" t="str">
         <v>138</v>
       </c>
-      <c r="B139" t="n">
+      <c r="B139" t="str">
         <v>54</v>
       </c>
-      <c r="C139" t="n">
-        <v>1</v>
-      </c>
-      <c r="D139" t="n">
+      <c r="C139" t="str">
+        <v>1</v>
+      </c>
+      <c r="D139" t="str">
         <v>100.57</v>
       </c>
-      <c r="E139" t="n">
+      <c r="E139" t="str">
         <v>524.812796</v>
       </c>
-      <c r="F139" t="n">
+      <c r="F139" t="str">
         <v>-21.877799</v>
       </c>
-      <c r="G139" t="n">
+      <c r="G139" t="str">
         <v>569.943456</v>
       </c>
-      <c r="H139" t="n">
+      <c r="H139" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="n">
+      <c r="A140" t="str">
         <v>139</v>
       </c>
-      <c r="B140" t="n">
+      <c r="B140" t="str">
         <v>100</v>
       </c>
-      <c r="C140" t="n">
-        <v>1</v>
-      </c>
-      <c r="D140" t="n">
+      <c r="C140" t="str">
+        <v>1</v>
+      </c>
+      <c r="D140" t="str">
         <v>101.66</v>
       </c>
-      <c r="E140" t="n">
+      <c r="E140" t="str">
         <v>436.052368</v>
       </c>
-      <c r="F140" t="n">
+      <c r="F140" t="str">
         <v>-293.232146</v>
       </c>
-      <c r="G140" t="n">
+      <c r="G140" t="str">
         <v>210.010429</v>
       </c>
-      <c r="H140" t="n">
+      <c r="H140" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="n">
+      <c r="A141" t="str">
         <v>140</v>
       </c>
-      <c r="B141" t="n">
+      <c r="B141" t="str">
         <v>108</v>
       </c>
-      <c r="C141" t="n">
-        <v>1</v>
-      </c>
-      <c r="D141" t="n">
+      <c r="C141" t="str">
+        <v>1</v>
+      </c>
+      <c r="D141" t="str">
         <v>103.68</v>
       </c>
-      <c r="E141" t="n">
+      <c r="E141" t="str">
         <v>525.1057089999999</v>
       </c>
-      <c r="F141" t="n">
+      <c r="F141" t="str">
         <v>-0.808161</v>
       </c>
-      <c r="G141" t="n">
+      <c r="G141" t="str">
         <v>150.599499</v>
       </c>
-      <c r="H141" t="n">
+      <c r="H141" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="n">
+      <c r="A142" t="str">
         <v>141</v>
       </c>
-      <c r="B142" t="n">
+      <c r="B142" t="str">
         <v>52</v>
       </c>
-      <c r="C142" t="n">
-        <v>1</v>
-      </c>
-      <c r="D142" t="n">
+      <c r="C142" t="str">
+        <v>1</v>
+      </c>
+      <c r="D142" t="str">
         <v>103.81</v>
       </c>
-      <c r="E142" t="n">
+      <c r="E142" t="str">
         <v>524.133775</v>
       </c>
-      <c r="F142" t="n">
+      <c r="F142" t="str">
         <v>-34.324366</v>
       </c>
-      <c r="G142" t="n">
+      <c r="G142" t="str">
         <v>146.863806</v>
       </c>
-      <c r="H142" t="n">
+      <c r="H142" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="n">
+      <c r="A143" t="str">
         <v>142</v>
       </c>
-      <c r="B143" t="n">
+      <c r="B143" t="str">
         <v>17</v>
       </c>
-      <c r="C143" t="n">
-        <v>1</v>
-      </c>
-      <c r="D143" t="n">
+      <c r="C143" t="str">
+        <v>1</v>
+      </c>
+      <c r="D143" t="str">
         <v>106.44</v>
       </c>
-      <c r="E143" t="n">
+      <c r="E143" t="str">
         <v>510.524793</v>
       </c>
-      <c r="F143" t="n">
+      <c r="F143" t="str">
         <v>-125.599406</v>
       </c>
-      <c r="G143" t="n">
+      <c r="G143" t="str">
         <v>417.255998</v>
       </c>
-      <c r="H143" t="n">
+      <c r="H143" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="n">
+      <c r="A144" t="str">
         <v>143</v>
       </c>
-      <c r="B144" t="n">
+      <c r="B144" t="str">
         <v>19</v>
       </c>
-      <c r="C144" t="n">
-        <v>1</v>
-      </c>
-      <c r="D144" t="n">
+      <c r="C144" t="str">
+        <v>1</v>
+      </c>
+      <c r="D144" t="str">
         <v>119.73</v>
       </c>
-      <c r="E144" t="n">
+      <c r="E144" t="str">
         <v>32.459384</v>
       </c>
-      <c r="F144" t="n">
+      <c r="F144" t="str">
         <v>524.070703</v>
       </c>
-      <c r="G144" t="n">
+      <c r="G144" t="str">
         <v>366.405324</v>
       </c>
-      <c r="H144" t="n">
+      <c r="H144" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="n">
+      <c r="A145" t="str">
         <v>144</v>
       </c>
-      <c r="B145" t="n">
+      <c r="B145" t="str">
         <v>56</v>
       </c>
-      <c r="C145" t="n">
-        <v>1</v>
-      </c>
-      <c r="D145" t="n">
+      <c r="C145" t="str">
+        <v>1</v>
+      </c>
+      <c r="D145" t="str">
         <v>120.6</v>
       </c>
-      <c r="E145" t="n">
+      <c r="E145" t="str">
         <v>525.08602</v>
       </c>
-      <c r="F145" t="n">
+      <c r="F145" t="str">
         <v>-6.002297</v>
       </c>
-      <c r="G145" t="n">
+      <c r="G145" t="str">
         <v>287.243236</v>
       </c>
-      <c r="H145" t="n">
+      <c r="H145" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="n">
+      <c r="A146" t="str">
         <v>145</v>
       </c>
-      <c r="B146" t="n">
+      <c r="B146" t="str">
         <v>6</v>
       </c>
-      <c r="C146" t="n">
-        <v>1</v>
-      </c>
-      <c r="D146" t="n">
+      <c r="C146" t="str">
+        <v>1</v>
+      </c>
+      <c r="D146" t="str">
         <v>124.31</v>
       </c>
-      <c r="E146" t="n">
+      <c r="E146" t="str">
         <v>200.509079</v>
       </c>
-      <c r="F146" t="n">
+      <c r="F146" t="str">
         <v>-485.333149</v>
       </c>
-      <c r="G146" t="n">
+      <c r="G146" t="str">
         <v>218.576862</v>
       </c>
-      <c r="H146" t="n">
+      <c r="H146" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="n">
+      <c r="A147" t="str">
         <v>146</v>
       </c>
-      <c r="B147" t="n">
+      <c r="B147" t="str">
         <v>188</v>
       </c>
-      <c r="C147" t="n">
-        <v>1</v>
-      </c>
-      <c r="D147" t="n">
+      <c r="C147" t="str">
+        <v>1</v>
+      </c>
+      <c r="D147" t="str">
         <v>126.86</v>
       </c>
-      <c r="E147" t="n">
+      <c r="E147" t="str">
         <v>516.236969</v>
       </c>
-      <c r="F147" t="n">
+      <c r="F147" t="str">
         <v>96.677403</v>
       </c>
-      <c r="G147" t="n">
+      <c r="G147" t="str">
         <v>283.052442</v>
       </c>
-      <c r="H147" t="n">
+      <c r="H147" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="n">
+      <c r="A148" t="str">
         <v>147</v>
       </c>
-      <c r="B148" t="n">
+      <c r="B148" t="str">
         <v>178</v>
       </c>
-      <c r="C148" t="n">
-        <v>1</v>
-      </c>
-      <c r="D148" t="n">
+      <c r="C148" t="str">
+        <v>1</v>
+      </c>
+      <c r="D148" t="str">
         <v>129.28</v>
       </c>
-      <c r="E148" t="n">
+      <c r="E148" t="str">
         <v>459.889001</v>
       </c>
-      <c r="F148" t="n">
+      <c r="F148" t="str">
         <v>-253.840785999999</v>
       </c>
-      <c r="G148" t="n">
+      <c r="G148" t="str">
         <v>457.3549400000001</v>
       </c>
-      <c r="H148" t="n">
+      <c r="H148" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="n">
+      <c r="A149" t="str">
         <v>148</v>
       </c>
-      <c r="B149" t="n">
+      <c r="B149" t="str">
         <v>144</v>
       </c>
-      <c r="C149" t="n">
-        <v>1</v>
-      </c>
-      <c r="D149" t="n">
+      <c r="C149" t="str">
+        <v>1</v>
+      </c>
+      <c r="D149" t="str">
         <v>130.14</v>
       </c>
-      <c r="E149" t="n">
+      <c r="E149" t="str">
         <v>523.479812</v>
       </c>
-      <c r="F149" t="n">
+      <c r="F149" t="str">
         <v>-45.134814</v>
       </c>
-      <c r="G149" t="n">
+      <c r="G149" t="str">
         <v>474.756783</v>
       </c>
-      <c r="H149" t="n">
+      <c r="H149" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="n">
+      <c r="A150" t="str">
         <v>149</v>
       </c>
-      <c r="B150" t="n">
+      <c r="B150" t="str">
         <v>165</v>
       </c>
-      <c r="C150" t="n">
-        <v>1</v>
-      </c>
-      <c r="D150" t="n">
+      <c r="C150" t="str">
+        <v>1</v>
+      </c>
+      <c r="D150" t="str">
         <v>141.73</v>
       </c>
-      <c r="E150" t="n">
+      <c r="E150" t="str">
         <v>517.802501</v>
       </c>
-      <c r="F150" t="n">
+      <c r="F150" t="str">
         <v>88.16416</v>
       </c>
-      <c r="G150" t="n">
+      <c r="G150" t="str">
         <v>132.007989</v>
       </c>
-      <c r="H150" t="n">
+      <c r="H150" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="n">
+      <c r="A151" t="str">
         <v>150</v>
       </c>
-      <c r="B151" t="n">
+      <c r="B151" t="str">
         <v>93</v>
       </c>
-      <c r="C151" t="n">
-        <v>1</v>
-      </c>
-      <c r="D151" t="n">
+      <c r="C151" t="str">
+        <v>1</v>
+      </c>
+      <c r="D151" t="str">
         <v>157.97</v>
       </c>
-      <c r="E151" t="n">
+      <c r="E151" t="str">
         <v>524.93623</v>
       </c>
-      <c r="F151" t="n">
+      <c r="F151" t="str">
         <v>23.685552</v>
       </c>
-      <c r="G151" t="n">
+      <c r="G151" t="str">
         <v>424.227001</v>
       </c>
-      <c r="H151" t="n">
+      <c r="H151" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="n">
+      <c r="A152" t="str">
         <v>151</v>
       </c>
-      <c r="B152" t="n">
+      <c r="B152" t="str">
         <v>198</v>
       </c>
-      <c r="C152" t="n">
-        <v>1</v>
-      </c>
-      <c r="D152" t="n">
+      <c r="C152" t="str">
+        <v>1</v>
+      </c>
+      <c r="D152" t="str">
         <v>161.54</v>
       </c>
-      <c r="E152" t="n">
+      <c r="E152" t="str">
         <v>523.341638</v>
       </c>
-      <c r="F152" t="n">
+      <c r="F152" t="str">
         <v>-42.394107</v>
       </c>
-      <c r="G152" t="n">
+      <c r="G152" t="str">
         <v>441.229721</v>
       </c>
-      <c r="H152" t="n">
+      <c r="H152" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="n">
+      <c r="A153" t="str">
         <v>152</v>
       </c>
-      <c r="B153" t="n">
+      <c r="B153" t="str">
         <v>12</v>
       </c>
-      <c r="C153" t="n">
-        <v>1</v>
-      </c>
-      <c r="D153" t="n">
+      <c r="C153" t="str">
+        <v>1</v>
+      </c>
+      <c r="D153" t="str">
         <v>161.73</v>
       </c>
-      <c r="E153" t="n">
+      <c r="E153" t="str">
         <v>463.230442</v>
       </c>
-      <c r="F153" t="n">
+      <c r="F153" t="str">
         <v>-247.137327</v>
       </c>
-      <c r="G153" t="n">
+      <c r="G153" t="str">
         <v>598.506569</v>
       </c>
-      <c r="H153" t="n">
+      <c r="H153" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="n">
+      <c r="A154" t="str">
         <v>153</v>
       </c>
-      <c r="B154" t="n">
+      <c r="B154" t="str">
         <v>130</v>
       </c>
-      <c r="C154" t="n">
-        <v>1</v>
-      </c>
-      <c r="D154" t="n">
+      <c r="C154" t="str">
+        <v>1</v>
+      </c>
+      <c r="D154" t="str">
         <v>162.9</v>
       </c>
-      <c r="E154" t="n">
+      <c r="E154" t="str">
         <v>446.55112</v>
       </c>
-      <c r="F154" t="n">
+      <c r="F154" t="str">
         <v>276.639092</v>
       </c>
-      <c r="G154" t="n">
+      <c r="G154" t="str">
         <v>416.713165</v>
       </c>
-      <c r="H154" t="n">
+      <c r="H154" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="n">
+      <c r="A155" t="str">
         <v>154</v>
       </c>
-      <c r="B155" t="n">
+      <c r="B155" t="str">
         <v>18</v>
       </c>
-      <c r="C155" t="n">
-        <v>1</v>
-      </c>
-      <c r="D155" t="n">
+      <c r="C155" t="str">
+        <v>1</v>
+      </c>
+      <c r="D155" t="str">
         <v>172.64</v>
       </c>
-      <c r="E155" t="n">
+      <c r="E155" t="str">
         <v>374.825509</v>
       </c>
-      <c r="F155" t="n">
+      <c r="F155" t="str">
         <v>367.822753</v>
       </c>
-      <c r="G155" t="n">
+      <c r="G155" t="str">
         <v>145.34321</v>
       </c>
-      <c r="H155" t="n">
+      <c r="H155" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="n">
+      <c r="A156" t="str">
         <v>155</v>
       </c>
-      <c r="B156" t="n">
+      <c r="B156" t="str">
         <v>59</v>
       </c>
-      <c r="C156" t="n">
-        <v>1</v>
-      </c>
-      <c r="D156" t="n">
+      <c r="C156" t="str">
+        <v>1</v>
+      </c>
+      <c r="D156" t="str">
         <v>179.84</v>
       </c>
-      <c r="E156" t="n">
+      <c r="E156" t="str">
         <v>440.64019</v>
       </c>
-      <c r="F156" t="n">
+      <c r="F156" t="str">
         <v>-285.575435</v>
       </c>
-      <c r="G156" t="n">
+      <c r="G156" t="str">
         <v>329.750019</v>
       </c>
-      <c r="H156" t="n">
+      <c r="H156" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="n">
+      <c r="A157" t="str">
         <v>156</v>
       </c>
-      <c r="B157" t="n">
+      <c r="B157" t="str">
         <v>128</v>
       </c>
-      <c r="C157" t="n">
-        <v>1</v>
-      </c>
-      <c r="D157" t="n">
+      <c r="C157" t="str">
+        <v>1</v>
+      </c>
+      <c r="D157" t="str">
         <v>186.87</v>
       </c>
-      <c r="E157" t="n">
+      <c r="E157" t="str">
         <v>503.871591</v>
       </c>
-      <c r="F157" t="n">
+      <c r="F157" t="str">
         <v>-147.963586</v>
       </c>
-      <c r="G157" t="n">
+      <c r="G157" t="str">
         <v>489.3968</v>
       </c>
-      <c r="H157" t="n">
+      <c r="H157" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="n">
+      <c r="A158" t="str">
         <v>157</v>
       </c>
-      <c r="B158" t="n">
+      <c r="B158" t="str">
         <v>55</v>
       </c>
-      <c r="C158" t="n">
-        <v>1</v>
-      </c>
-      <c r="D158" t="n">
+      <c r="C158" t="str">
+        <v>1</v>
+      </c>
+      <c r="D158" t="str">
         <v>188.67</v>
       </c>
-      <c r="E158" t="n">
+      <c r="E158" t="str">
         <v>511.0521480000001</v>
       </c>
-      <c r="F158" t="n">
+      <c r="F158" t="str">
         <v>-122.003348</v>
       </c>
-      <c r="G158" t="n">
+      <c r="G158" t="str">
         <v>122.088376</v>
       </c>
-      <c r="H158" t="n">
+      <c r="H158" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="n">
+      <c r="A159" t="str">
         <v>158</v>
       </c>
-      <c r="B159" t="n">
+      <c r="B159" t="str">
         <v>143</v>
       </c>
-      <c r="C159" t="n">
-        <v>1</v>
-      </c>
-      <c r="D159" t="n">
+      <c r="C159" t="str">
+        <v>1</v>
+      </c>
+      <c r="D159" t="str">
         <v>192.01</v>
       </c>
-      <c r="E159" t="n">
+      <c r="E159" t="str">
         <v>469.589246</v>
       </c>
-      <c r="F159" t="n">
+      <c r="F159" t="str">
         <v>-235.255741</v>
       </c>
-      <c r="G159" t="n">
+      <c r="G159" t="str">
         <v>285.443172</v>
       </c>
-      <c r="H159" t="n">
+      <c r="H159" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="n">
+      <c r="A160" t="str">
         <v>159</v>
       </c>
-      <c r="B160" t="n">
+      <c r="B160" t="str">
         <v>99</v>
       </c>
-      <c r="C160" t="n">
-        <v>1</v>
-      </c>
-      <c r="D160" t="n">
+      <c r="C160" t="str">
+        <v>1</v>
+      </c>
+      <c r="D160" t="str">
         <v>192.08</v>
       </c>
-      <c r="E160" t="n">
+      <c r="E160" t="str">
         <v>434.887508</v>
       </c>
-      <c r="F160" t="n">
+      <c r="F160" t="str">
         <v>294.839663</v>
       </c>
-      <c r="G160" t="n">
+      <c r="G160" t="str">
         <v>118.243656</v>
       </c>
-      <c r="H160" t="n">
+      <c r="H160" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="n">
+      <c r="A161" t="str">
         <v>160</v>
       </c>
-      <c r="B161" t="n">
+      <c r="B161" t="str">
         <v>171</v>
       </c>
-      <c r="C161" t="n">
-        <v>1</v>
-      </c>
-      <c r="D161" t="n">
+      <c r="C161" t="str">
+        <v>1</v>
+      </c>
+      <c r="D161" t="str">
         <v>214.49</v>
       </c>
-      <c r="E161" t="n">
+      <c r="E161" t="str">
         <v>519.211307</v>
       </c>
-      <c r="F161" t="n">
-        <v>-77.90040399999999</v>
-      </c>
-      <c r="G161" t="n">
+      <c r="F161" t="str">
+        <v>-77.900404</v>
+      </c>
+      <c r="G161" t="str">
         <v>549.8170660000001</v>
       </c>
-      <c r="H161" t="n">
+      <c r="H161" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="n">
+      <c r="A162" t="str">
         <v>161</v>
       </c>
-      <c r="B162" t="n">
+      <c r="B162" t="str">
         <v>10</v>
       </c>
-      <c r="C162" t="n">
-        <v>1</v>
-      </c>
-      <c r="D162" t="n">
+      <c r="C162" t="str">
+        <v>1</v>
+      </c>
+      <c r="D162" t="str">
         <v>219.73</v>
       </c>
-      <c r="E162" t="n">
+      <c r="E162" t="str">
         <v>397.50664</v>
       </c>
-      <c r="F162" t="n">
+      <c r="F162" t="str">
         <v>343.957741</v>
       </c>
-      <c r="G162" t="n">
+      <c r="G162" t="str">
         <v>220.415185</v>
       </c>
-      <c r="H162" t="n">
+      <c r="H162" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="n">
+      <c r="A163" t="str">
         <v>162</v>
       </c>
-      <c r="B163" t="n">
+      <c r="B163" t="str">
         <v>116</v>
       </c>
-      <c r="C163" t="n">
-        <v>1</v>
-      </c>
-      <c r="D163" t="n">
+      <c r="C163" t="str">
+        <v>1</v>
+      </c>
+      <c r="D163" t="str">
         <v>231.76</v>
       </c>
-      <c r="E163" t="n">
+      <c r="E163" t="str">
         <v>482.800103</v>
       </c>
-      <c r="F163" t="n">
+      <c r="F163" t="str">
         <v>-207.350104</v>
       </c>
-      <c r="G163" t="n">
+      <c r="G163" t="str">
         <v>535.069801</v>
       </c>
-      <c r="H163" t="n">
+      <c r="H163" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="n">
+      <c r="A164" t="str">
         <v>163</v>
       </c>
-      <c r="B164" t="n">
+      <c r="B164" t="str">
         <v>9</v>
       </c>
-      <c r="C164" t="n">
-        <v>1</v>
-      </c>
-      <c r="D164" t="n">
+      <c r="C164" t="str">
+        <v>1</v>
+      </c>
+      <c r="D164" t="str">
         <v>241.76</v>
       </c>
-      <c r="E164" t="n">
+      <c r="E164" t="str">
         <v>483.341559</v>
       </c>
-      <c r="F164" t="n">
+      <c r="F164" t="str">
         <v>206.390346</v>
       </c>
-      <c r="G164" t="n">
+      <c r="G164" t="str">
         <v>368.886707</v>
       </c>
-      <c r="H164" t="n">
+      <c r="H164" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="n">
+      <c r="A165" t="str">
         <v>164</v>
       </c>
-      <c r="B165" t="n">
+      <c r="B165" t="str">
         <v>66</v>
       </c>
-      <c r="C165" t="n">
-        <v>1</v>
-      </c>
-      <c r="D165" t="n">
+      <c r="C165" t="str">
+        <v>1</v>
+      </c>
+      <c r="D165" t="str">
         <v>275.68</v>
       </c>
-      <c r="E165" t="n">
+      <c r="E165" t="str">
         <v>406.444514</v>
       </c>
-      <c r="F165" t="n">
+      <c r="F165" t="str">
         <v>-332.697656</v>
       </c>
-      <c r="G165" t="n">
+      <c r="G165" t="str">
         <v>378.340129</v>
       </c>
-      <c r="H165" t="n">
+      <c r="H165" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="n">
+      <c r="A166" t="str">
         <v>165</v>
       </c>
-      <c r="B166" t="n">
+      <c r="B166" t="str">
         <v>83</v>
       </c>
-      <c r="C166" t="n">
-        <v>1</v>
-      </c>
-      <c r="D166" t="n">
+      <c r="C166" t="str">
+        <v>1</v>
+      </c>
+      <c r="D166" t="str">
         <v>286.57</v>
       </c>
-      <c r="E166" t="n">
+      <c r="E166" t="str">
         <v>493.068627</v>
       </c>
-      <c r="F166" t="n">
+      <c r="F166" t="str">
         <v>-181.007473</v>
       </c>
-      <c r="G166" t="n">
+      <c r="G166" t="str">
         <v>148.298139</v>
       </c>
-      <c r="H166" t="n">
+      <c r="H166" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="n">
+      <c r="A167" t="str">
         <v>166</v>
       </c>
-      <c r="B167" t="n">
+      <c r="B167" t="str">
         <v>5</v>
       </c>
-      <c r="C167" t="n">
-        <v>1</v>
-      </c>
-      <c r="D167" t="n">
+      <c r="C167" t="str">
+        <v>1</v>
+      </c>
+      <c r="D167" t="str">
         <v>301.61</v>
       </c>
-      <c r="E167" t="n">
+      <c r="E167" t="str">
         <v>425.775318</v>
       </c>
-      <c r="F167" t="n">
+      <c r="F167" t="str">
         <v>-308.269741</v>
       </c>
-      <c r="G167" t="n">
+      <c r="G167" t="str">
         <v>378.280952</v>
       </c>
-      <c r="H167" t="n">
+      <c r="H167" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="n">
+      <c r="A168" t="str">
         <v>167</v>
       </c>
-      <c r="B168" t="n">
+      <c r="B168" t="str">
         <v>35</v>
       </c>
-      <c r="C168" t="n">
-        <v>1</v>
-      </c>
-      <c r="D168" t="n">
+      <c r="C168" t="str">
+        <v>1</v>
+      </c>
+      <c r="D168" t="str">
         <v>313.38</v>
       </c>
-      <c r="E168" t="n">
+      <c r="E168" t="str">
         <v>495.948273</v>
       </c>
-      <c r="F168" t="n">
+      <c r="F168" t="str">
         <v>172.863842</v>
       </c>
-      <c r="G168" t="n">
+      <c r="G168" t="str">
         <v>417.033803</v>
       </c>
-      <c r="H168" t="n">
+      <c r="H168" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="n">
+      <c r="A169" t="str">
         <v>168</v>
       </c>
-      <c r="B169" t="n">
+      <c r="B169" t="str">
         <v>81</v>
       </c>
-      <c r="C169" t="n">
-        <v>1</v>
-      </c>
-      <c r="D169" t="n">
+      <c r="C169" t="str">
+        <v>1</v>
+      </c>
+      <c r="D169" t="str">
         <v>335.8</v>
       </c>
-      <c r="E169" t="n">
+      <c r="E169" t="str">
         <v>425.901429</v>
       </c>
-      <c r="F169" t="n">
+      <c r="F169" t="str">
         <v>-307.318302999999</v>
       </c>
-      <c r="G169" t="n">
+      <c r="G169" t="str">
         <v>496.710066</v>
       </c>
-      <c r="H169" t="n">
+      <c r="H169" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="n">
+      <c r="A170" t="str">
         <v>169</v>
       </c>
-      <c r="B170" t="n">
+      <c r="B170" t="str">
         <v>151</v>
       </c>
-      <c r="C170" t="n">
-        <v>1</v>
-      </c>
-      <c r="D170" t="n">
+      <c r="C170" t="str">
+        <v>1</v>
+      </c>
+      <c r="D170" t="str">
         <v>401.5</v>
       </c>
-      <c r="E170" t="n">
+      <c r="E170" t="str">
         <v>472.21133</v>
       </c>
-      <c r="F170" t="n">
+      <c r="F170" t="str">
         <v>230.423846</v>
       </c>
-      <c r="G170" t="n">
+      <c r="G170" t="str">
         <v>132.380917</v>
       </c>
-      <c r="H170" t="n">
+      <c r="H170" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="n">
+      <c r="A171" t="str">
         <v>170</v>
       </c>
-      <c r="B171" t="n">
+      <c r="B171" t="str">
         <v>140</v>
       </c>
-      <c r="C171" t="n">
-        <v>1</v>
-      </c>
-      <c r="D171" t="n">
+      <c r="C171" t="str">
+        <v>1</v>
+      </c>
+      <c r="D171" t="str">
         <v>443.77</v>
       </c>
-      <c r="E171" t="n">
+      <c r="E171" t="str">
         <v>518.787235</v>
       </c>
-      <c r="F171" t="n">
+      <c r="F171" t="str">
         <v>-82.286571</v>
       </c>
-      <c r="G171" t="n">
+      <c r="G171" t="str">
         <v>377.252186</v>
       </c>
-      <c r="H171" t="n">
+      <c r="H171" t="str">
         <v>0</v>
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="n">
+      <c r="A172" t="str">
         <v>171</v>
       </c>
-      <c r="B172" t="n">
+      <c r="B172" t="str">
         <v>21</v>
       </c>
-      <c r="C172" t="n">
-        <v>1</v>
-      </c>
-      <c r="D172" t="n">
-        <v>539.8200000000001</v>
-      </c>
-      <c r="E172" t="n">
+      <c r="C172" t="str">
+        <v>1</v>
+      </c>
+      <c r="D172" t="str">
+        <v>539.82</v>
+      </c>
+      <c r="E172" t="str">
         <v>474.995091</v>
       </c>
-      <c r="F172" t="n">
+      <c r="F172" t="str">
         <v>-224.763487</v>
       </c>
-      <c r="G172" t="n">
+      <c r="G172" t="str">
         <v>149.763753</v>
       </c>
-      <c r="H172" t="n">
+      <c r="H172" t="str">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H172"/>
+  </ignoredErrors>
 </worksheet>
 </file>